--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9673</v>
+        <v>0.967</v>
       </c>
       <c r="F2" t="n">
-        <v>200.2792</v>
+        <v>200.7538</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>423.668</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9799</v>
+        <v>0.9806</v>
       </c>
       <c r="F3" t="n">
-        <v>160.5216</v>
+        <v>157.8983</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>412.6417</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9823</v>
+        <v>0.9821</v>
       </c>
       <c r="F4" t="n">
-        <v>160.8517</v>
+        <v>161.3524</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>474.6909</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8713</v>
+        <v>0.8719</v>
       </c>
       <c r="F5" t="n">
-        <v>419.4057</v>
+        <v>419.5097</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>713.9073</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.869</v>
+        <v>0.8702</v>
       </c>
       <c r="F6" t="n">
-        <v>420.9582</v>
+        <v>419.639</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>715.4061</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9804</v>
       </c>
       <c r="F7" t="n">
-        <v>157.1827</v>
+        <v>156.021</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>433.258</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9766</v>
+        <v>0.977</v>
       </c>
       <c r="F8" t="n">
-        <v>178.0036</v>
+        <v>175.6802</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>444.841</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9785</v>
+        <v>0.9804</v>
       </c>
       <c r="F9" t="n">
-        <v>172.781</v>
+        <v>164.8024</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>410.4059</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9842</v>
+        <v>0.984</v>
       </c>
       <c r="F10" t="n">
-        <v>147.9676</v>
+        <v>147.9169</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>445.1285</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9843</v>
       </c>
       <c r="F11" t="n">
-        <v>146.7621</v>
+        <v>146.5047</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>445.477</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>0.9842</v>
       </c>
       <c r="F12" t="n">
-        <v>147.7267</v>
+        <v>147.2732</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>445.2339</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.984</v>
+        <v>0.9841</v>
       </c>
       <c r="F13" t="n">
-        <v>147.9585</v>
+        <v>148.4183</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>443.6503</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9843</v>
+        <v>0.9842</v>
       </c>
       <c r="F14" t="n">
-        <v>147.0308</v>
+        <v>146.7023</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>445.2461</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9843</v>
+        <v>0.9842</v>
       </c>
       <c r="F15" t="n">
-        <v>147.6926</v>
+        <v>147.4557</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>444.599</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>0.9842</v>
       </c>
       <c r="F16" t="n">
-        <v>148.0782</v>
+        <v>147.1845</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>444.8562</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>0.984</v>
       </c>
       <c r="F17" t="n">
-        <v>148.2035</v>
+        <v>147.9941</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>444.1293</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9861</v>
+        <v>0.986</v>
       </c>
       <c r="F18" t="n">
-        <v>135.6257</v>
+        <v>136.043</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>404.9604</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9848</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>142.0939</v>
+        <v>139.6176</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>403.8992</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9848</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>144.1484</v>
+        <v>141.0133</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>411.7022</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9792</v>
+        <v>0.979</v>
       </c>
       <c r="F21" t="n">
-        <v>166.2428</v>
+        <v>167.9038</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>407.5318</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>0.9854000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>142.4653</v>
+        <v>142.3683</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>411.6842</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9851</v>
+        <v>0.9775</v>
       </c>
       <c r="F23" t="n">
-        <v>143.2133</v>
+        <v>171.5005</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>410.8961</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.985</v>
+        <v>0.9788</v>
       </c>
       <c r="F24" t="n">
-        <v>144.2088</v>
+        <v>164.2641</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>409.3448</v>
       </c>
     </row>
     <row r="25">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.985</v>
+        <v>0.9849</v>
       </c>
       <c r="F25" t="n">
-        <v>141.7968</v>
+        <v>141.9197</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>410.884</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9852</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>136.7019</v>
+        <v>136.6344</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>402.1511</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>0.9862</v>
       </c>
       <c r="F27" t="n">
-        <v>133.9734</v>
+        <v>133.391</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>403.8685</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.986</v>
+        <v>0.9855</v>
       </c>
       <c r="F28" t="n">
-        <v>132.7862</v>
+        <v>141.3462</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>404.2323</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9852</v>
+        <v>0.985</v>
       </c>
       <c r="F29" t="n">
-        <v>138.6532</v>
+        <v>139.2087</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>404.2812</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9851</v>
+        <v>0.9848</v>
       </c>
       <c r="F30" t="n">
-        <v>144.5569</v>
+        <v>146.1242</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>412.1081</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9849</v>
+        <v>0.9855</v>
       </c>
       <c r="F31" t="n">
-        <v>143.925</v>
+        <v>141.6188</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>406.3004</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9853</v>
       </c>
       <c r="F32" t="n">
-        <v>137.4561</v>
+        <v>138.4268</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>414.52</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9751</v>
       </c>
       <c r="F33" t="n">
-        <v>179.3051</v>
+        <v>179.4309</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>410.1763</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9826</v>
+        <v>0.9822</v>
       </c>
       <c r="F34" t="n">
-        <v>151.6932</v>
+        <v>153.7732</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>407.9706</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9871</v>
+        <v>0.9832</v>
       </c>
       <c r="F35" t="n">
-        <v>126.9436</v>
+        <v>147.616</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>401.0735</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9807</v>
+        <v>0.9805</v>
       </c>
       <c r="F36" t="n">
-        <v>161.1458</v>
+        <v>161.828</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>410.3696</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9794</v>
       </c>
       <c r="F37" t="n">
-        <v>137.0094</v>
+        <v>164.1887</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>405.1309</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9858</v>
+        <v>0.9796</v>
       </c>
       <c r="F38" t="n">
-        <v>133.4489</v>
+        <v>156.8508</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>394.4848</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9868</v>
+        <v>0.9865</v>
       </c>
       <c r="F39" t="n">
-        <v>126.5965</v>
+        <v>128.3985</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>389.3393</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.98</v>
+        <v>0.9801</v>
       </c>
       <c r="F40" t="n">
-        <v>161.0887</v>
+        <v>160.8333</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>401.752</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9827</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>151.2614</v>
+        <v>153.1325</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>406.4702</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>0.9829</v>
       </c>
       <c r="F42" t="n">
-        <v>148.7045</v>
+        <v>148.6142</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>401.0895</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9855</v>
+        <v>0.9767</v>
       </c>
       <c r="F43" t="n">
-        <v>140.8193</v>
+        <v>173.4741</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>412.504</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9871</v>
+        <v>0.9792</v>
       </c>
       <c r="F44" t="n">
-        <v>134.6667</v>
+        <v>165.5054</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>402.0329</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9859</v>
       </c>
       <c r="F45" t="n">
-        <v>130.6651</v>
+        <v>132.5788</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>393.1609</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9862</v>
       </c>
       <c r="F46" t="n">
-        <v>128.9034</v>
+        <v>129.935</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>391.0158</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.985</v>
+        <v>0.9848</v>
       </c>
       <c r="F47" t="n">
-        <v>135.2328</v>
+        <v>136.2343</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>404.0427</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9856</v>
+        <v>0.9858</v>
       </c>
       <c r="F48" t="n">
-        <v>142.9602</v>
+        <v>142.5415</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>422.1723</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9801</v>
+        <v>0.9791</v>
       </c>
       <c r="F49" t="n">
-        <v>166.0743</v>
+        <v>170.3968</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>412.2557</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9071</v>
+        <v>0.9066</v>
       </c>
       <c r="F50" t="n">
-        <v>395.0813</v>
+        <v>395.067</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>696.4018</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>0.8891</v>
       </c>
       <c r="F51" t="n">
-        <v>406.5535</v>
+        <v>406.3867</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>682.8269</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8516</v>
+        <v>0.8517</v>
       </c>
       <c r="F52" t="n">
-        <v>456.5729</v>
+        <v>456.4132</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>687.6368</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>0.8965</v>
       </c>
       <c r="F53" t="n">
-        <v>413.0169</v>
+        <v>413.1405</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>677.4751</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8908</v>
       </c>
       <c r="F54" t="n">
-        <v>408.1268</v>
+        <v>408.04</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>665.8663</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8923</v>
+        <v>0.8924</v>
       </c>
       <c r="F55" t="n">
-        <v>408.0582</v>
+        <v>408.8399</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>694.8193</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>0.8673999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>448.6458</v>
+        <v>448.6497</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>699.189</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9051</v>
+        <v>0.9049</v>
       </c>
       <c r="F57" t="n">
-        <v>397.8611</v>
+        <v>398.0218</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>693.8007</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8702</v>
+        <v>0.8716</v>
       </c>
       <c r="F58" t="n">
-        <v>419.8842</v>
+        <v>418.6837</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>715.4686</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8517</v>
+        <v>0.8512</v>
       </c>
       <c r="F59" t="n">
-        <v>446.6777</v>
+        <v>446.721</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>714.4402</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8448</v>
+        <v>0.8968</v>
       </c>
       <c r="F60" t="n">
-        <v>446.8347</v>
+        <v>387.6151</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>715.16</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8454</v>
+        <v>0.8447</v>
       </c>
       <c r="F61" t="n">
-        <v>446.5866</v>
+        <v>446.8274</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>714.6968000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8747</v>
+        <v>0.8754</v>
       </c>
       <c r="F62" t="n">
-        <v>423.4786</v>
+        <v>423.1379</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>709.0806</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>0.8363</v>
       </c>
       <c r="F63" t="n">
-        <v>463.9225</v>
+        <v>463.8268</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>711.1494</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.835</v>
+        <v>0.8351</v>
       </c>
       <c r="F64" t="n">
-        <v>463.9501</v>
+        <v>463.8705</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>711.4977</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8335</v>
+        <v>0.8337</v>
       </c>
       <c r="F65" t="n">
-        <v>465.0153</v>
+        <v>464.8421</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>712.3913</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8944</v>
+        <v>0.8938</v>
       </c>
       <c r="F66" t="n">
-        <v>409.1263</v>
+        <v>409.5181</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>695.1832000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9049</v>
+        <v>0.9053</v>
       </c>
       <c r="F67" t="n">
-        <v>394.0056</v>
+        <v>393.9802</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>692.2776</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9025</v>
+        <v>0.9029</v>
       </c>
       <c r="F68" t="n">
-        <v>396.6962</v>
+        <v>396.5331</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>695.6547</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9847</v>
+        <v>0.9849</v>
       </c>
       <c r="F69" t="n">
-        <v>140.1401</v>
+        <v>139.0723</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>402.1119</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9836</v>
+        <v>0.9838</v>
       </c>
       <c r="F70" t="n">
-        <v>147.48</v>
+        <v>147.0194</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>402.3024</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9852</v>
       </c>
       <c r="F71" t="n">
-        <v>140.0966</v>
+        <v>142.361</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>411.8588</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>0.9842</v>
       </c>
       <c r="F72" t="n">
-        <v>143.7683</v>
+        <v>144.5152</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>406.3976</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>0.9842</v>
       </c>
       <c r="F73" t="n">
-        <v>153.1537</v>
+        <v>153.1528</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>432.8146</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9615</v>
+        <v>0.9598</v>
       </c>
       <c r="F74" t="n">
-        <v>215.25</v>
+        <v>218.4171</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>423.1718</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.973</v>
+        <v>0.9821</v>
       </c>
       <c r="F75" t="n">
-        <v>185.3434</v>
+        <v>153.353</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>458.1532</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.973</v>
+        <v>0.9821</v>
       </c>
       <c r="F76" t="n">
-        <v>185.3434</v>
+        <v>153.353</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>458.1532</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8536</v>
+        <v>0.9452</v>
       </c>
       <c r="F77" t="n">
-        <v>440.4001</v>
+        <v>318.9557</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>711.1856</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8562</v>
+        <v>0.8963</v>
       </c>
       <c r="F78" t="n">
-        <v>435.5419</v>
+        <v>387.8435</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>711.9616</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8116</v>
+        <v>0.8573</v>
       </c>
       <c r="F79" t="n">
-        <v>481.3203</v>
+        <v>434.3888</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>713.0408</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8981</v>
+        <v>0.8962</v>
       </c>
       <c r="F80" t="n">
-        <v>386.0386</v>
+        <v>387.9052</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>711.1697</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8441</v>
+        <v>0.8444</v>
       </c>
       <c r="F81" t="n">
-        <v>458.5886</v>
+        <v>458.4593</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>701.6174999999999</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>0.8491</v>
       </c>
       <c r="F82" t="n">
-        <v>453.8126</v>
+        <v>453.8315</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>700.5838</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9825</v>
+        <v>0.9817</v>
       </c>
       <c r="F83" t="n">
-        <v>152.2334</v>
+        <v>154.2998</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>458.4513</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9817</v>
       </c>
       <c r="F84" t="n">
-        <v>152.3178</v>
+        <v>154.2895</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>457.1123</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9811</v>
+        <v>0.9818</v>
       </c>
       <c r="F85" t="n">
-        <v>156.1153</v>
+        <v>154.1882</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>459.6075</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9853</v>
+        <v>0.9846</v>
       </c>
       <c r="F86" t="n">
-        <v>138.205</v>
+        <v>141.0575</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>407.5843</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9808</v>
       </c>
       <c r="F87" t="n">
-        <v>142.6928</v>
+        <v>157.6598</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>412.9119</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.984</v>
+        <v>0.979</v>
       </c>
       <c r="F88" t="n">
-        <v>143.9347</v>
+        <v>162.8857</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>414.6046</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9847</v>
+        <v>0.9786</v>
       </c>
       <c r="F89" t="n">
-        <v>141.3127</v>
+        <v>166.0664</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>428.3391</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9853</v>
+        <v>0.9767</v>
       </c>
       <c r="F90" t="n">
-        <v>141.6155</v>
+        <v>173.4741</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>412.5228</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9871</v>
+        <v>0.9792</v>
       </c>
       <c r="F91" t="n">
-        <v>134.6648</v>
+        <v>165.5054</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>402.034</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.984</v>
+        <v>0.979</v>
       </c>
       <c r="F92" t="n">
-        <v>143.9347</v>
+        <v>162.8857</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>414.6046</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9871</v>
+        <v>0.9792</v>
       </c>
       <c r="F93" t="n">
-        <v>134.6648</v>
+        <v>165.5054</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>402.034</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9823</v>
+        <v>0.9821</v>
       </c>
       <c r="F94" t="n">
-        <v>160.8517</v>
+        <v>161.3524</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>474.6909</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>0.7972</v>
       </c>
       <c r="F95" t="n">
-        <v>532.2320999999999</v>
+        <v>532.3154</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>794.253</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9825</v>
+        <v>0.9823</v>
       </c>
       <c r="F96" t="n">
-        <v>159.7374</v>
+        <v>160.2295</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>475.1086</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9826</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F97" t="n">
-        <v>159.408</v>
+        <v>159.8229</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>474.7348</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
         <v>0.9873</v>
       </c>
       <c r="F98" t="n">
-        <v>140.5015</v>
+        <v>139.8011</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>406.348</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9873</v>
+        <v>0.9869</v>
       </c>
       <c r="F99" t="n">
-        <v>137.7306</v>
+        <v>138.6736</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>404.15</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>0.9869</v>
       </c>
       <c r="F100" t="n">
-        <v>138.8848</v>
+        <v>139.1557</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>405.3764</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9867</v>
+        <v>0.9866</v>
       </c>
       <c r="F101" t="n">
-        <v>139.6977</v>
+        <v>140.6831</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>408.736</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9863</v>
+        <v>0.9862</v>
       </c>
       <c r="F102" t="n">
-        <v>140.6679</v>
+        <v>141.0485</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>412.1191</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9876</v>
+        <v>0.9875</v>
       </c>
       <c r="F103" t="n">
-        <v>139.362</v>
+        <v>138.6462</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>409.0801</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9871</v>
+        <v>0.9869</v>
       </c>
       <c r="F104" t="n">
-        <v>140.7017</v>
+        <v>140.6354</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>406.6542</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9772</v>
+        <v>0.9771</v>
       </c>
       <c r="F105" t="n">
-        <v>175.2121</v>
+        <v>176.2734</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>405.5289</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9871</v>
+        <v>0.9868</v>
       </c>
       <c r="F106" t="n">
-        <v>138.8447</v>
+        <v>140.0551</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>405.0721</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9865</v>
+        <v>0.9863</v>
       </c>
       <c r="F107" t="n">
-        <v>139.6667</v>
+        <v>140.7095</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>408.9332</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9759</v>
+        <v>0.975</v>
       </c>
       <c r="F108" t="n">
-        <v>189.0642</v>
+        <v>191.799</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>445.4706</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9835</v>
+        <v>0.9839</v>
       </c>
       <c r="F109" t="n">
-        <v>156.4591</v>
+        <v>155.5727</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>411.0667</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9792</v>
+        <v>0.9846</v>
       </c>
       <c r="F110" t="n">
-        <v>164.741</v>
+        <v>142.7864</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>410.9707</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F111" t="n">
-        <v>168.2533</v>
+        <v>171.3365</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>411.6282</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.985</v>
+        <v>0.9848</v>
       </c>
       <c r="F112" t="n">
-        <v>154.3245</v>
+        <v>154.3992</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>443.3702</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9836</v>
+        <v>0.984</v>
       </c>
       <c r="F113" t="n">
-        <v>156.6548</v>
+        <v>155.5095</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>411.485</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9851</v>
+        <v>0.9798</v>
       </c>
       <c r="F114" t="n">
-        <v>142.3711</v>
+        <v>162.1036</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>411.7709</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9784</v>
+        <v>0.9859</v>
       </c>
       <c r="F115" t="n">
-        <v>167.7616</v>
+        <v>146.6426</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>410.7345</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8854</v>
+        <v>0.8855</v>
       </c>
       <c r="F116" t="n">
-        <v>407.967</v>
+        <v>407.6548</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>713.5441</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.8837</v>
       </c>
       <c r="F117" t="n">
-        <v>408.6085</v>
+        <v>408.8045</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>713.5264</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9772</v>
+        <v>0.9771</v>
       </c>
       <c r="F118" t="n">
-        <v>175.2121</v>
+        <v>176.2734</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>405.5289</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9836</v>
+        <v>0.984</v>
       </c>
       <c r="F119" t="n">
-        <v>156.6548</v>
+        <v>155.5095</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>411.485</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>266.8077</v>
+        <v>195.4517</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>423.3378</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>266.8077</v>
+        <v>195.4517</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>423.3378</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9837</v>
+        <v>0.9651</v>
       </c>
       <c r="F122" t="n">
-        <v>140.9889</v>
+        <v>199.4662</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>390.0987</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9836</v>
+        <v>0.984</v>
       </c>
       <c r="F123" t="n">
-        <v>156.7668</v>
+        <v>155.5907</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>412.0081</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9853</v>
+        <v>0.9866</v>
       </c>
       <c r="F124" t="n">
-        <v>144.3075</v>
+        <v>141.4007</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>412.3005</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9667</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F125" t="n">
-        <v>209.0528</v>
+        <v>209.6701</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>478.5414</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9853</v>
+        <v>0.9856</v>
       </c>
       <c r="F126" t="n">
-        <v>135.6811</v>
+        <v>135.9838</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>402.4174</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.7906</v>
+        <v>0.7909</v>
       </c>
       <c r="F127" t="n">
-        <v>506.9046</v>
+        <v>506.7163</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>742.2674</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9838</v>
+        <v>0.9836</v>
       </c>
       <c r="F128" t="n">
-        <v>143.8335</v>
+        <v>146.1011</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>413.9786</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
         <v>0.9844000000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>141.6137</v>
+        <v>141.6096</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>416.5998</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9831</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>146.5479</v>
+        <v>138.9333</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>417.6493</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9862</v>
+        <v>0.986</v>
       </c>
       <c r="F131" t="n">
-        <v>139.5689</v>
+        <v>140.5252</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>417.8385</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.985</v>
       </c>
       <c r="F132" t="n">
-        <v>135.9465</v>
+        <v>138.5526</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>403.6386</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9853</v>
+        <v>0.9855</v>
       </c>
       <c r="F133" t="n">
-        <v>136.694</v>
+        <v>136.4423</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>408.2317</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9852</v>
+        <v>0.9851</v>
       </c>
       <c r="F134" t="n">
-        <v>136.8657</v>
+        <v>138.6933</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>407.8127</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.985</v>
+        <v>0.9846</v>
       </c>
       <c r="F135" t="n">
-        <v>138.9828</v>
+        <v>141.4099</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>410.0399</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9862</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>139.5765</v>
+        <v>141.3175</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>413.761</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9851</v>
+        <v>0.9849</v>
       </c>
       <c r="F137" t="n">
-        <v>137.6833</v>
+        <v>137.4266</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>399.4991</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9849</v>
+        <v>0.9837</v>
       </c>
       <c r="F138" t="n">
-        <v>136.7092</v>
+        <v>141.4904</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>395.7546</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9845</v>
+        <v>0.9846</v>
       </c>
       <c r="F139" t="n">
-        <v>138.8495</v>
+        <v>139.8186</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>396.0884</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
         <v>0.9804</v>
       </c>
       <c r="F140" t="n">
-        <v>160.0725</v>
+        <v>159.6285</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>390.8841</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9867</v>
+        <v>0.9828</v>
       </c>
       <c r="F141" t="n">
-        <v>135.9637</v>
+        <v>147.976</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>389.4902</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9849</v>
+        <v>0.9837</v>
       </c>
       <c r="F142" t="n">
-        <v>136.7092</v>
+        <v>141.4904</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>395.7546</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.976</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>169.8941</v>
+        <v>169.0301</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>394.7946</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9846</v>
+        <v>0.9847</v>
       </c>
       <c r="F144" t="n">
-        <v>138.9401</v>
+        <v>139.6542</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>400.0851</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9867</v>
+        <v>0.9828</v>
       </c>
       <c r="F145" t="n">
-        <v>135.9637</v>
+        <v>147.976</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>389.4902</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7921</v>
       </c>
       <c r="F146" t="n">
-        <v>505.9552</v>
+        <v>505.7545</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>741.6064</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.7935</v>
+        <v>0.7936</v>
       </c>
       <c r="F147" t="n">
-        <v>504.4634</v>
+        <v>504.3034</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>740.8022999999999</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
         <v>0.7938</v>
       </c>
       <c r="F148" t="n">
-        <v>504.7354</v>
+        <v>504.5749</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>741.7617</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.8454</v>
       </c>
       <c r="F149" t="n">
-        <v>503.6855</v>
+        <v>457.171</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>742.1499</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.79</v>
+        <v>0.7904</v>
       </c>
       <c r="F150" t="n">
-        <v>507.298</v>
+        <v>507.0519</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>741.5744</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.7922</v>
+        <v>0.7925</v>
       </c>
       <c r="F151" t="n">
-        <v>506.0244</v>
+        <v>505.8393</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>741.9429</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.7932</v>
+        <v>0.7936</v>
       </c>
       <c r="F152" t="n">
-        <v>505.4016</v>
+        <v>505.1203</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>742.2204</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.7926</v>
+        <v>0.793</v>
       </c>
       <c r="F153" t="n">
-        <v>505.7805</v>
+        <v>505.5168</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>742.6058</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8434</v>
+        <v>0.7916</v>
       </c>
       <c r="F154" t="n">
-        <v>462.2249</v>
+        <v>506.358</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>741.7726</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8484</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="F155" t="n">
-        <v>460.0831</v>
+        <v>460.0744</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>705.8313000000001</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
         <v>0.8404</v>
       </c>
       <c r="F156" t="n">
-        <v>464.1513</v>
+        <v>464.1396</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>710.914</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.84</v>
+        <v>0.8399</v>
       </c>
       <c r="F157" t="n">
-        <v>463.7568</v>
+        <v>463.7489</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>709.3092</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.8541</v>
       </c>
       <c r="F158" t="n">
-        <v>457.4608</v>
+        <v>457.4726</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>696.1299</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9873</v>
+        <v>0.9872</v>
       </c>
       <c r="F159" t="n">
-        <v>127.9709</v>
+        <v>128.4378</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>387.3087</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8507</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="F160" t="n">
-        <v>451.5736</v>
+        <v>451.1679</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>732.2422</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8466</v>
+        <v>0.8462</v>
       </c>
       <c r="F161" t="n">
-        <v>456.6826</v>
+        <v>456.7384</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>734.7424</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9873</v>
+        <v>0.9876</v>
       </c>
       <c r="F162" t="n">
-        <v>130.0075</v>
+        <v>129.0899</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>392.449</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9851</v>
+        <v>0.9856</v>
       </c>
       <c r="F163" t="n">
-        <v>137.618</v>
+        <v>137.4742</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>401.6111</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
         <v>0.9804</v>
       </c>
       <c r="F164" t="n">
-        <v>160.1</v>
+        <v>159.6571</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>391.529</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9667</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F165" t="n">
-        <v>209.0528</v>
+        <v>209.6701</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>478.5414</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7963</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="F166" t="n">
-        <v>531.7089999999999</v>
+        <v>531.7619</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>794.2306</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9772</v>
+        <v>0.9863</v>
       </c>
       <c r="F167" t="n">
-        <v>167.9447</v>
+        <v>135.1389</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>394.3533</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9861</v>
+        <v>0.9871</v>
       </c>
       <c r="F168" t="n">
-        <v>135.0626</v>
+        <v>133.0159</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>380.6285</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9648</v>
+        <v>0.984</v>
       </c>
       <c r="F169" t="n">
-        <v>205.1136</v>
+        <v>144.015</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>424.1137</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.985</v>
+        <v>0.9847</v>
       </c>
       <c r="F170" t="n">
-        <v>148.7954</v>
+        <v>147.8144</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>441.1947</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F171" t="n">
-        <v>140.8942</v>
+        <v>144.9906</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>406.369</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9802</v>
+        <v>0.9808</v>
       </c>
       <c r="F172" t="n">
-        <v>158.6353</v>
+        <v>155.307</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>400.6169</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.967</v>
       </c>
       <c r="F2" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="G2" t="n">
         <v>200.7538</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>423.668</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9806</v>
       </c>
       <c r="F3" t="n">
+        <v>1.3086</v>
+      </c>
+      <c r="G3" t="n">
         <v>157.8983</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>412.6417</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9821</v>
       </c>
       <c r="F4" t="n">
+        <v>1.4083</v>
+      </c>
+      <c r="G4" t="n">
         <v>161.3524</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>474.6909</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.8719</v>
       </c>
       <c r="F5" t="n">
+        <v>1.9236</v>
+      </c>
+      <c r="G5" t="n">
         <v>419.5097</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>713.9073</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.8702</v>
       </c>
       <c r="F6" t="n">
+        <v>1.9275</v>
+      </c>
+      <c r="G6" t="n">
         <v>419.639</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>715.4061</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.9804</v>
       </c>
       <c r="F7" t="n">
+        <v>1.3402</v>
+      </c>
+      <c r="G7" t="n">
         <v>156.021</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>433.258</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.977</v>
       </c>
       <c r="F8" t="n">
+        <v>1.3586</v>
+      </c>
+      <c r="G8" t="n">
         <v>175.6802</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>444.841</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9804</v>
       </c>
       <c r="F9" t="n">
+        <v>1.3052</v>
+      </c>
+      <c r="G9" t="n">
         <v>164.8024</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>410.4059</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.984</v>
       </c>
       <c r="F10" t="n">
+        <v>1.3591</v>
+      </c>
+      <c r="G10" t="n">
         <v>147.9169</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>445.1285</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.9843</v>
       </c>
       <c r="F11" t="n">
+        <v>1.3596</v>
+      </c>
+      <c r="G11" t="n">
         <v>146.5047</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>445.477</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.9842</v>
       </c>
       <c r="F12" t="n">
+        <v>1.3592</v>
+      </c>
+      <c r="G12" t="n">
         <v>147.2732</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>445.2339</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9841</v>
       </c>
       <c r="F13" t="n">
+        <v>1.3567</v>
+      </c>
+      <c r="G13" t="n">
         <v>148.4183</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>443.6503</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.9842</v>
       </c>
       <c r="F14" t="n">
+        <v>1.3592</v>
+      </c>
+      <c r="G14" t="n">
         <v>146.7023</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>445.2461</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9842</v>
       </c>
       <c r="F15" t="n">
+        <v>1.3582</v>
+      </c>
+      <c r="G15" t="n">
         <v>147.4557</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>444.599</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.9842</v>
       </c>
       <c r="F16" t="n">
+        <v>1.3586</v>
+      </c>
+      <c r="G16" t="n">
         <v>147.1845</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>444.8562</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.984</v>
       </c>
       <c r="F17" t="n">
+        <v>1.3574</v>
+      </c>
+      <c r="G17" t="n">
         <v>147.9941</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>444.1293</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.986</v>
       </c>
       <c r="F18" t="n">
+        <v>1.2972</v>
+      </c>
+      <c r="G18" t="n">
         <v>136.043</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>404.9604</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F19" t="n">
+        <v>1.2956</v>
+      </c>
+      <c r="G19" t="n">
         <v>139.6176</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>403.8992</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F20" t="n">
+        <v>1.3072</v>
+      </c>
+      <c r="G20" t="n">
         <v>141.0133</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>411.7022</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.979</v>
       </c>
       <c r="F21" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="G21" t="n">
         <v>167.9038</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>407.5318</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F22" t="n">
+        <v>1.3071</v>
+      </c>
+      <c r="G22" t="n">
         <v>142.3683</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>411.6842</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9775</v>
       </c>
       <c r="F23" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="G23" t="n">
         <v>171.5005</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>410.8961</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.9788</v>
       </c>
       <c r="F24" t="n">
+        <v>1.3036</v>
+      </c>
+      <c r="G24" t="n">
         <v>164.2641</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>409.3448</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9849</v>
       </c>
       <c r="F25" t="n">
+        <v>1.3059</v>
+      </c>
+      <c r="G25" t="n">
         <v>141.9197</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>410.884</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.9854000000000001</v>
       </c>
       <c r="F26" t="n">
+        <v>1.2931</v>
+      </c>
+      <c r="G26" t="n">
         <v>136.6344</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>402.1511</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9862</v>
       </c>
       <c r="F27" t="n">
+        <v>1.2956</v>
+      </c>
+      <c r="G27" t="n">
         <v>133.391</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>403.8685</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9855</v>
       </c>
       <c r="F28" t="n">
+        <v>1.2961</v>
+      </c>
+      <c r="G28" t="n">
         <v>141.3462</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>404.2323</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.985</v>
       </c>
       <c r="F29" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="G29" t="n">
         <v>139.2087</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>404.2812</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9848</v>
       </c>
       <c r="F30" t="n">
+        <v>1.3078</v>
+      </c>
+      <c r="G30" t="n">
         <v>146.1242</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>412.1081</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9855</v>
       </c>
       <c r="F31" t="n">
+        <v>1.2991</v>
+      </c>
+      <c r="G31" t="n">
         <v>141.6188</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>406.3004</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9853</v>
       </c>
       <c r="F32" t="n">
+        <v>1.3114</v>
+      </c>
+      <c r="G32" t="n">
         <v>138.4268</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>414.52</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9751</v>
       </c>
       <c r="F33" t="n">
+        <v>1.3049</v>
+      </c>
+      <c r="G33" t="n">
         <v>179.4309</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>410.1763</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9822</v>
       </c>
       <c r="F34" t="n">
+        <v>1.3016</v>
+      </c>
+      <c r="G34" t="n">
         <v>153.7732</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>407.9706</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9832</v>
       </c>
       <c r="F35" t="n">
+        <v>1.2915</v>
+      </c>
+      <c r="G35" t="n">
         <v>147.616</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>401.0735</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9805</v>
       </c>
       <c r="F36" t="n">
+        <v>1.3052</v>
+      </c>
+      <c r="G36" t="n">
         <v>161.828</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>410.3696</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9794</v>
       </c>
       <c r="F37" t="n">
+        <v>1.2974</v>
+      </c>
+      <c r="G37" t="n">
         <v>164.1887</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>405.1309</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9796</v>
       </c>
       <c r="F38" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="G38" t="n">
         <v>156.8508</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>394.4848</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9865</v>
       </c>
       <c r="F39" t="n">
+        <v>1.2747</v>
+      </c>
+      <c r="G39" t="n">
         <v>128.3985</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>389.3393</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.9801</v>
       </c>
       <c r="F40" t="n">
+        <v>1.2925</v>
+      </c>
+      <c r="G40" t="n">
         <v>160.8333</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>401.752</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="F41" t="n">
+        <v>1.2994</v>
+      </c>
+      <c r="G41" t="n">
         <v>153.1325</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>406.4702</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9829</v>
       </c>
       <c r="F42" t="n">
+        <v>1.2915</v>
+      </c>
+      <c r="G42" t="n">
         <v>148.6142</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>401.0895</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9767</v>
       </c>
       <c r="F43" t="n">
+        <v>1.3084</v>
+      </c>
+      <c r="G43" t="n">
         <v>173.4741</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>412.504</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9792</v>
       </c>
       <c r="F44" t="n">
+        <v>1.2929</v>
+      </c>
+      <c r="G44" t="n">
         <v>165.5054</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>402.0329</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9859</v>
       </c>
       <c r="F45" t="n">
+        <v>1.2801</v>
+      </c>
+      <c r="G45" t="n">
         <v>132.5788</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>393.1609</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9862</v>
       </c>
       <c r="F46" t="n">
+        <v>1.2771</v>
+      </c>
+      <c r="G46" t="n">
         <v>129.935</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>391.0158</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.9848</v>
       </c>
       <c r="F47" t="n">
+        <v>1.2958</v>
+      </c>
+      <c r="G47" t="n">
         <v>136.2343</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>404.0427</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.9858</v>
       </c>
       <c r="F48" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="G48" t="n">
         <v>142.5415</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>422.1723</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9791</v>
       </c>
       <c r="F49" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="G49" t="n">
         <v>170.3968</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>412.2557</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.9066</v>
       </c>
       <c r="F50" t="n">
+        <v>1.8788</v>
+      </c>
+      <c r="G50" t="n">
         <v>395.067</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>696.4018</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.8891</v>
       </c>
       <c r="F51" t="n">
+        <v>1.8449</v>
+      </c>
+      <c r="G51" t="n">
         <v>406.3867</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>682.8269</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.8517</v>
       </c>
       <c r="F52" t="n">
+        <v>1.8569</v>
+      </c>
+      <c r="G52" t="n">
         <v>456.4132</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>687.6368</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.8965</v>
       </c>
       <c r="F53" t="n">
+        <v>1.8317</v>
+      </c>
+      <c r="G53" t="n">
         <v>413.1405</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>677.4751</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.8908</v>
       </c>
       <c r="F54" t="n">
+        <v>1.8035</v>
+      </c>
+      <c r="G54" t="n">
         <v>408.04</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>665.8663</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.8924</v>
       </c>
       <c r="F55" t="n">
+        <v>1.8749</v>
+      </c>
+      <c r="G55" t="n">
         <v>408.8399</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>694.8193</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.8673999999999999</v>
       </c>
       <c r="F56" t="n">
+        <v>1.8859</v>
+      </c>
+      <c r="G56" t="n">
         <v>448.6497</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>699.189</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.9049</v>
       </c>
       <c r="F57" t="n">
+        <v>1.8723</v>
+      </c>
+      <c r="G57" t="n">
         <v>398.0218</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>693.8007</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.8716</v>
       </c>
       <c r="F58" t="n">
+        <v>1.9276</v>
+      </c>
+      <c r="G58" t="n">
         <v>418.6837</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>715.4686</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.8512</v>
       </c>
       <c r="F59" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="G59" t="n">
         <v>446.721</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>714.4402</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.8968</v>
       </c>
       <c r="F60" t="n">
+        <v>1.9268</v>
+      </c>
+      <c r="G60" t="n">
         <v>387.6151</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>715.16</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.8447</v>
       </c>
       <c r="F61" t="n">
+        <v>1.9256</v>
+      </c>
+      <c r="G61" t="n">
         <v>446.8274</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>714.6968000000001</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.8754</v>
       </c>
       <c r="F62" t="n">
+        <v>1.9111</v>
+      </c>
+      <c r="G62" t="n">
         <v>423.1379</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>709.0806</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.8363</v>
       </c>
       <c r="F63" t="n">
+        <v>1.9165</v>
+      </c>
+      <c r="G63" t="n">
         <v>463.8268</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>711.1494</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.8351</v>
       </c>
       <c r="F64" t="n">
+        <v>1.9174</v>
+      </c>
+      <c r="G64" t="n">
         <v>463.8705</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>711.4977</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.8337</v>
       </c>
       <c r="F65" t="n">
+        <v>1.9197</v>
+      </c>
+      <c r="G65" t="n">
         <v>464.8421</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>712.3913</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.8938</v>
       </c>
       <c r="F66" t="n">
+        <v>1.8758</v>
+      </c>
+      <c r="G66" t="n">
         <v>409.5181</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>695.1832000000001</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.9053</v>
       </c>
       <c r="F67" t="n">
+        <v>1.8685</v>
+      </c>
+      <c r="G67" t="n">
         <v>393.9802</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>692.2776</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.9029</v>
       </c>
       <c r="F68" t="n">
+        <v>1.877</v>
+      </c>
+      <c r="G68" t="n">
         <v>396.5331</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>695.6547</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9849</v>
       </c>
       <c r="F69" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="G69" t="n">
         <v>139.0723</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>402.1119</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9838</v>
       </c>
       <c r="F70" t="n">
+        <v>1.2933</v>
+      </c>
+      <c r="G70" t="n">
         <v>147.0194</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>402.3024</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9852</v>
       </c>
       <c r="F71" t="n">
+        <v>1.3074</v>
+      </c>
+      <c r="G71" t="n">
         <v>142.361</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>411.8588</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9842</v>
       </c>
       <c r="F72" t="n">
+        <v>1.2993</v>
+      </c>
+      <c r="G72" t="n">
         <v>144.5152</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>406.3976</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9842</v>
       </c>
       <c r="F73" t="n">
+        <v>1.3395</v>
+      </c>
+      <c r="G73" t="n">
         <v>153.1528</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>432.8146</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9598</v>
       </c>
       <c r="F74" t="n">
+        <v>1.3245</v>
+      </c>
+      <c r="G74" t="n">
         <v>218.4171</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>423.1718</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9821</v>
       </c>
       <c r="F75" t="n">
+        <v>1.3804</v>
+      </c>
+      <c r="G75" t="n">
         <v>153.353</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>458.1532</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9821</v>
       </c>
       <c r="F76" t="n">
+        <v>1.3804</v>
+      </c>
+      <c r="G76" t="n">
         <v>153.353</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>458.1532</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.9452</v>
       </c>
       <c r="F77" t="n">
+        <v>1.9166</v>
+      </c>
+      <c r="G77" t="n">
         <v>318.9557</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>711.1856</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.8963</v>
       </c>
       <c r="F78" t="n">
+        <v>1.9186</v>
+      </c>
+      <c r="G78" t="n">
         <v>387.8435</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>711.9616</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.8573</v>
       </c>
       <c r="F79" t="n">
+        <v>1.9213</v>
+      </c>
+      <c r="G79" t="n">
         <v>434.3888</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>713.0408</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.8962</v>
       </c>
       <c r="F80" t="n">
+        <v>1.9165</v>
+      </c>
+      <c r="G80" t="n">
         <v>387.9052</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>711.1697</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.8444</v>
       </c>
       <c r="F81" t="n">
+        <v>1.8921</v>
+      </c>
+      <c r="G81" t="n">
         <v>458.4593</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>701.6174999999999</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.8491</v>
       </c>
       <c r="F82" t="n">
+        <v>1.8894</v>
+      </c>
+      <c r="G82" t="n">
         <v>453.8315</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>700.5838</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.9817</v>
       </c>
       <c r="F83" t="n">
+        <v>1.3809</v>
+      </c>
+      <c r="G83" t="n">
         <v>154.2998</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>458.4513</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.9817</v>
       </c>
       <c r="F84" t="n">
+        <v>1.3787</v>
+      </c>
+      <c r="G84" t="n">
         <v>154.2895</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>457.1123</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.9818</v>
       </c>
       <c r="F85" t="n">
+        <v>1.3828</v>
+      </c>
+      <c r="G85" t="n">
         <v>154.1882</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>459.6075</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9846</v>
       </c>
       <c r="F86" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="G86" t="n">
         <v>141.0575</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>407.5843</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9808</v>
       </c>
       <c r="F87" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="G87" t="n">
         <v>157.6598</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>412.9119</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.979</v>
       </c>
       <c r="F88" t="n">
+        <v>1.3115</v>
+      </c>
+      <c r="G88" t="n">
         <v>162.8857</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>414.6046</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9786</v>
       </c>
       <c r="F89" t="n">
+        <v>1.3325</v>
+      </c>
+      <c r="G89" t="n">
         <v>166.0664</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>428.3391</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9767</v>
       </c>
       <c r="F90" t="n">
+        <v>1.3084</v>
+      </c>
+      <c r="G90" t="n">
         <v>173.4741</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>412.5228</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9792</v>
       </c>
       <c r="F91" t="n">
+        <v>1.2929</v>
+      </c>
+      <c r="G91" t="n">
         <v>165.5054</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>402.034</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.979</v>
       </c>
       <c r="F92" t="n">
+        <v>1.3115</v>
+      </c>
+      <c r="G92" t="n">
         <v>162.8857</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>414.6046</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9792</v>
       </c>
       <c r="F93" t="n">
+        <v>1.2929</v>
+      </c>
+      <c r="G93" t="n">
         <v>165.5054</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>402.034</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9821</v>
       </c>
       <c r="F94" t="n">
+        <v>1.4083</v>
+      </c>
+      <c r="G94" t="n">
         <v>161.3524</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>474.6909</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.7972</v>
       </c>
       <c r="F95" t="n">
+        <v>2.1432</v>
+      </c>
+      <c r="G95" t="n">
         <v>532.3154</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>794.253</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9823</v>
       </c>
       <c r="F96" t="n">
+        <v>1.4091</v>
+      </c>
+      <c r="G96" t="n">
         <v>160.2295</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>475.1086</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="F97" t="n">
+        <v>1.4084</v>
+      </c>
+      <c r="G97" t="n">
         <v>159.8229</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>474.7348</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9873</v>
       </c>
       <c r="F98" t="n">
+        <v>1.2992</v>
+      </c>
+      <c r="G98" t="n">
         <v>139.8011</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>406.348</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9869</v>
       </c>
       <c r="F99" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="G99" t="n">
         <v>138.6736</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>404.15</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.9869</v>
       </c>
       <c r="F100" t="n">
+        <v>1.2978</v>
+      </c>
+      <c r="G100" t="n">
         <v>139.1557</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>405.3764</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9866</v>
       </c>
       <c r="F101" t="n">
+        <v>1.3027</v>
+      </c>
+      <c r="G101" t="n">
         <v>140.6831</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>408.736</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9862</v>
       </c>
       <c r="F102" t="n">
+        <v>1.3078</v>
+      </c>
+      <c r="G102" t="n">
         <v>141.0485</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>412.1191</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9875</v>
       </c>
       <c r="F103" t="n">
+        <v>1.3033</v>
+      </c>
+      <c r="G103" t="n">
         <v>138.6462</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>409.0801</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.9869</v>
       </c>
       <c r="F104" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="G104" t="n">
         <v>140.6354</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>406.6542</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9771</v>
       </c>
       <c r="F105" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="G105" t="n">
         <v>176.2734</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>405.5289</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9868</v>
       </c>
       <c r="F106" t="n">
+        <v>1.2973</v>
+      </c>
+      <c r="G106" t="n">
         <v>140.0551</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>405.0721</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9863</v>
       </c>
       <c r="F107" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="G107" t="n">
         <v>140.7095</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>408.9332</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.975</v>
       </c>
       <c r="F108" t="n">
+        <v>1.3596</v>
+      </c>
+      <c r="G108" t="n">
         <v>191.799</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>445.4706</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9839</v>
       </c>
       <c r="F109" t="n">
+        <v>1.3062</v>
+      </c>
+      <c r="G109" t="n">
         <v>155.5727</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>411.0667</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9846</v>
       </c>
       <c r="F110" t="n">
+        <v>1.3061</v>
+      </c>
+      <c r="G110" t="n">
         <v>142.7864</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>410.9707</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F111" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="G111" t="n">
         <v>171.3365</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>411.6282</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9848</v>
       </c>
       <c r="F112" t="n">
+        <v>1.3562</v>
+      </c>
+      <c r="G112" t="n">
         <v>154.3992</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>443.3702</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.984</v>
       </c>
       <c r="F113" t="n">
+        <v>1.3068</v>
+      </c>
+      <c r="G113" t="n">
         <v>155.5095</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>411.485</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9798</v>
       </c>
       <c r="F114" t="n">
+        <v>1.3073</v>
+      </c>
+      <c r="G114" t="n">
         <v>162.1036</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>411.7709</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9859</v>
       </c>
       <c r="F115" t="n">
+        <v>1.3057</v>
+      </c>
+      <c r="G115" t="n">
         <v>146.6426</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>410.7345</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.8855</v>
       </c>
       <c r="F116" t="n">
+        <v>1.9226</v>
+      </c>
+      <c r="G116" t="n">
         <v>407.6548</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>713.5441</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.8837</v>
       </c>
       <c r="F117" t="n">
+        <v>1.9226</v>
+      </c>
+      <c r="G117" t="n">
         <v>408.8045</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>713.5264</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9771</v>
       </c>
       <c r="F118" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="G118" t="n">
         <v>176.2734</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>405.5289</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.984</v>
       </c>
       <c r="F119" t="n">
+        <v>1.3068</v>
+      </c>
+      <c r="G119" t="n">
         <v>155.5095</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>411.485</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.9693000000000001</v>
       </c>
       <c r="F120" t="n">
+        <v>1.3248</v>
+      </c>
+      <c r="G120" t="n">
         <v>195.4517</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>423.3378</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.9693000000000001</v>
       </c>
       <c r="F121" t="n">
+        <v>1.3248</v>
+      </c>
+      <c r="G121" t="n">
         <v>195.4517</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>423.3378</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9651</v>
       </c>
       <c r="F122" t="n">
+        <v>1.2758</v>
+      </c>
+      <c r="G122" t="n">
         <v>199.4662</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>390.0987</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.984</v>
       </c>
       <c r="F123" t="n">
+        <v>1.3076</v>
+      </c>
+      <c r="G123" t="n">
         <v>155.5907</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>412.0081</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9866</v>
       </c>
       <c r="F124" t="n">
+        <v>1.3081</v>
+      </c>
+      <c r="G124" t="n">
         <v>141.4007</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>412.3005</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9661999999999999</v>
       </c>
       <c r="F125" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="G125" t="n">
         <v>209.6701</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>478.5414</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.9856</v>
       </c>
       <c r="F126" t="n">
+        <v>1.2935</v>
+      </c>
+      <c r="G126" t="n">
         <v>135.9838</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>402.4174</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.7909</v>
       </c>
       <c r="F127" t="n">
+        <v>1.9984</v>
+      </c>
+      <c r="G127" t="n">
         <v>506.7163</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>742.2674</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.9836</v>
       </c>
       <c r="F128" t="n">
+        <v>1.3106</v>
+      </c>
+      <c r="G128" t="n">
         <v>146.1011</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>413.9786</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.9844000000000001</v>
       </c>
       <c r="F129" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="G129" t="n">
         <v>141.6096</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>416.5998</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.9864000000000001</v>
       </c>
       <c r="F130" t="n">
+        <v>1.3161</v>
+      </c>
+      <c r="G130" t="n">
         <v>138.9333</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>417.6493</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.986</v>
       </c>
       <c r="F131" t="n">
+        <v>1.3164</v>
+      </c>
+      <c r="G131" t="n">
         <v>140.5252</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>417.8385</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.985</v>
       </c>
       <c r="F132" t="n">
+        <v>1.2952</v>
+      </c>
+      <c r="G132" t="n">
         <v>138.5526</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>403.6386</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.9855</v>
       </c>
       <c r="F133" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="G133" t="n">
         <v>136.4423</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>408.2317</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.9851</v>
       </c>
       <c r="F134" t="n">
+        <v>1.3014</v>
+      </c>
+      <c r="G134" t="n">
         <v>138.6933</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>407.8127</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.9846</v>
       </c>
       <c r="F135" t="n">
+        <v>1.3047</v>
+      </c>
+      <c r="G135" t="n">
         <v>141.4099</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>410.0399</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.9844000000000001</v>
       </c>
       <c r="F136" t="n">
+        <v>1.3102</v>
+      </c>
+      <c r="G136" t="n">
         <v>141.3175</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>413.761</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9849</v>
       </c>
       <c r="F137" t="n">
+        <v>1.2892</v>
+      </c>
+      <c r="G137" t="n">
         <v>137.4266</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>399.4991</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9837</v>
       </c>
       <c r="F138" t="n">
+        <v>1.2838</v>
+      </c>
+      <c r="G138" t="n">
         <v>141.4904</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>395.7546</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9846</v>
       </c>
       <c r="F139" t="n">
+        <v>1.2843</v>
+      </c>
+      <c r="G139" t="n">
         <v>139.8186</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>396.0884</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.9804</v>
       </c>
       <c r="F140" t="n">
+        <v>1.2769</v>
+      </c>
+      <c r="G140" t="n">
         <v>159.6285</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>390.8841</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9828</v>
       </c>
       <c r="F141" t="n">
+        <v>1.2749</v>
+      </c>
+      <c r="G141" t="n">
         <v>147.976</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>389.4902</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9837</v>
       </c>
       <c r="F142" t="n">
+        <v>1.2838</v>
+      </c>
+      <c r="G142" t="n">
         <v>141.4904</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>395.7546</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9762999999999999</v>
       </c>
       <c r="F143" t="n">
+        <v>1.2824</v>
+      </c>
+      <c r="G143" t="n">
         <v>169.0301</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>394.7946</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9847</v>
       </c>
       <c r="F144" t="n">
+        <v>1.2901</v>
+      </c>
+      <c r="G144" t="n">
         <v>139.6542</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>400.0851</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9828</v>
       </c>
       <c r="F145" t="n">
+        <v>1.2749</v>
+      </c>
+      <c r="G145" t="n">
         <v>147.976</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>389.4902</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.7921</v>
       </c>
       <c r="F146" t="n">
+        <v>1.9966</v>
+      </c>
+      <c r="G146" t="n">
         <v>505.7545</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>741.6064</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.7936</v>
       </c>
       <c r="F147" t="n">
+        <v>1.9945</v>
+      </c>
+      <c r="G147" t="n">
         <v>504.3034</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>740.8022999999999</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.7938</v>
       </c>
       <c r="F148" t="n">
+        <v>1.9971</v>
+      </c>
+      <c r="G148" t="n">
         <v>504.5749</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>741.7617</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.8454</v>
       </c>
       <c r="F149" t="n">
+        <v>1.9981</v>
+      </c>
+      <c r="G149" t="n">
         <v>457.171</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>742.1499</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.7904</v>
       </c>
       <c r="F150" t="n">
+        <v>1.9966</v>
+      </c>
+      <c r="G150" t="n">
         <v>507.0519</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>741.5744</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.7925</v>
       </c>
       <c r="F151" t="n">
+        <v>1.9975</v>
+      </c>
+      <c r="G151" t="n">
         <v>505.8393</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>741.9429</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.7936</v>
       </c>
       <c r="F152" t="n">
+        <v>1.9983</v>
+      </c>
+      <c r="G152" t="n">
         <v>505.1203</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>742.2204</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.793</v>
       </c>
       <c r="F153" t="n">
+        <v>1.9993</v>
+      </c>
+      <c r="G153" t="n">
         <v>505.5168</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>742.6058</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.7916</v>
       </c>
       <c r="F154" t="n">
+        <v>1.9971</v>
+      </c>
+      <c r="G154" t="n">
         <v>506.358</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>741.7726</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.8483000000000001</v>
       </c>
       <c r="F155" t="n">
+        <v>1.9028</v>
+      </c>
+      <c r="G155" t="n">
         <v>460.0744</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>705.8313000000001</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.8404</v>
       </c>
       <c r="F156" t="n">
+        <v>1.9159</v>
+      </c>
+      <c r="G156" t="n">
         <v>464.1396</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>710.914</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.8399</v>
       </c>
       <c r="F157" t="n">
+        <v>1.9117</v>
+      </c>
+      <c r="G157" t="n">
         <v>463.7489</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>709.3092</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.8541</v>
       </c>
       <c r="F158" t="n">
+        <v>1.8782</v>
+      </c>
+      <c r="G158" t="n">
         <v>457.4726</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>696.1299</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.9872</v>
       </c>
       <c r="F159" t="n">
+        <v>1.2718</v>
+      </c>
+      <c r="G159" t="n">
         <v>128.4378</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>387.3087</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.8512999999999999</v>
       </c>
       <c r="F160" t="n">
+        <v>1.9716</v>
+      </c>
+      <c r="G160" t="n">
         <v>451.1679</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>732.2422</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.8462</v>
       </c>
       <c r="F161" t="n">
+        <v>1.9783</v>
+      </c>
+      <c r="G161" t="n">
         <v>456.7384</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>734.7424</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.9876</v>
       </c>
       <c r="F162" t="n">
+        <v>1.2791</v>
+      </c>
+      <c r="G162" t="n">
         <v>129.0899</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>392.449</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9856</v>
       </c>
       <c r="F163" t="n">
+        <v>1.2923</v>
+      </c>
+      <c r="G163" t="n">
         <v>137.4742</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>401.6111</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9804</v>
       </c>
       <c r="F164" t="n">
+        <v>1.2778</v>
+      </c>
+      <c r="G164" t="n">
         <v>159.6571</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>391.529</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9661999999999999</v>
       </c>
       <c r="F165" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="G165" t="n">
         <v>209.6701</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>478.5414</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.7959000000000001</v>
       </c>
       <c r="F166" t="n">
+        <v>2.1431</v>
+      </c>
+      <c r="G166" t="n">
         <v>531.7619</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>794.2306</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9863</v>
       </c>
       <c r="F167" t="n">
+        <v>1.2818</v>
+      </c>
+      <c r="G167" t="n">
         <v>135.1389</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>394.3533</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9871</v>
       </c>
       <c r="F168" t="n">
+        <v>1.2625</v>
+      </c>
+      <c r="G168" t="n">
         <v>133.0159</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>380.6285</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.984</v>
       </c>
       <c r="F169" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="G169" t="n">
         <v>144.015</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>424.1137</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9847</v>
       </c>
       <c r="F170" t="n">
+        <v>1.3527</v>
+      </c>
+      <c r="G170" t="n">
         <v>147.8144</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>441.1947</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9844000000000001</v>
       </c>
       <c r="F171" t="n">
+        <v>1.2993</v>
+      </c>
+      <c r="G171" t="n">
         <v>144.9906</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>406.369</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9808</v>
       </c>
       <c r="F172" t="n">
+        <v>1.2908</v>
+      </c>
+      <c r="G172" t="n">
         <v>155.307</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>400.6169</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.967</v>
+        <v>0.9762</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3253</v>
+        <v>0.676</v>
       </c>
       <c r="G2" t="n">
-        <v>200.7538</v>
+        <v>167.7212</v>
       </c>
       <c r="H2" t="n">
-        <v>423.668</v>
+        <v>413.0823</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9806</v>
+        <v>0.968</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3086</v>
+        <v>0.7229</v>
       </c>
       <c r="G3" t="n">
-        <v>157.8983</v>
+        <v>195.2358</v>
       </c>
       <c r="H3" t="n">
-        <v>412.6417</v>
+        <v>382.0009</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9821</v>
+        <v>0.9393</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4083</v>
+        <v>0.6384</v>
       </c>
       <c r="G4" t="n">
-        <v>161.3524</v>
+        <v>256.6862</v>
       </c>
       <c r="H4" t="n">
-        <v>474.6909</v>
+        <v>436.4298</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8719</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9236</v>
+        <v>-0.0413</v>
       </c>
       <c r="G5" t="n">
-        <v>419.5097</v>
+        <v>444.0839</v>
       </c>
       <c r="H5" t="n">
-        <v>713.9073</v>
+        <v>740.5685</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8702</v>
+        <v>0.8985</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9275</v>
+        <v>-0.0311</v>
       </c>
       <c r="G6" t="n">
-        <v>419.639</v>
+        <v>391.7431</v>
       </c>
       <c r="H6" t="n">
-        <v>715.4061</v>
+        <v>736.9446</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9804</v>
+        <v>0.9356</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3402</v>
+        <v>0.5978</v>
       </c>
       <c r="G7" t="n">
-        <v>156.021</v>
+        <v>261.8405</v>
       </c>
       <c r="H7" t="n">
-        <v>433.258</v>
+        <v>460.2408</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.977</v>
+        <v>0.9785</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3586</v>
+        <v>0.6428</v>
       </c>
       <c r="G8" t="n">
-        <v>175.6802</v>
+        <v>165.7261</v>
       </c>
       <c r="H8" t="n">
-        <v>444.841</v>
+        <v>433.7663</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9804</v>
+        <v>0.965</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3052</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>164.8024</v>
+        <v>201.0674</v>
       </c>
       <c r="H9" t="n">
-        <v>410.4059</v>
+        <v>376.9003</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.984</v>
+        <v>0.9717</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3591</v>
+        <v>0.6448</v>
       </c>
       <c r="G10" t="n">
-        <v>147.9169</v>
+        <v>188.898</v>
       </c>
       <c r="H10" t="n">
-        <v>445.1285</v>
+        <v>432.5363</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9843</v>
+        <v>0.9797</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3596</v>
+        <v>0.6439</v>
       </c>
       <c r="G11" t="n">
-        <v>146.5047</v>
+        <v>159.2554</v>
       </c>
       <c r="H11" t="n">
-        <v>445.477</v>
+        <v>433.096</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9842</v>
+        <v>0.9796</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3592</v>
+        <v>0.6534</v>
       </c>
       <c r="G12" t="n">
-        <v>147.2732</v>
+        <v>161.6381</v>
       </c>
       <c r="H12" t="n">
-        <v>445.2339</v>
+        <v>427.2739</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9841</v>
+        <v>0.9786</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3567</v>
+        <v>0.65</v>
       </c>
       <c r="G13" t="n">
-        <v>148.4183</v>
+        <v>164.5909</v>
       </c>
       <c r="H13" t="n">
-        <v>443.6503</v>
+        <v>429.3581</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9842</v>
+        <v>0.98</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3592</v>
+        <v>0.6423</v>
       </c>
       <c r="G14" t="n">
-        <v>146.7023</v>
+        <v>157.8937</v>
       </c>
       <c r="H14" t="n">
-        <v>445.2461</v>
+        <v>434.0417</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9842</v>
+        <v>0.9795</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3582</v>
+        <v>0.6562</v>
       </c>
       <c r="G15" t="n">
-        <v>147.4557</v>
+        <v>160.8255</v>
       </c>
       <c r="H15" t="n">
-        <v>444.599</v>
+        <v>425.4999</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9842</v>
+        <v>0.9796</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3586</v>
+        <v>0.6562</v>
       </c>
       <c r="G16" t="n">
-        <v>147.1845</v>
+        <v>160.1016</v>
       </c>
       <c r="H16" t="n">
-        <v>444.8562</v>
+        <v>425.5025</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.984</v>
+        <v>0.9782</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3574</v>
+        <v>0.655</v>
       </c>
       <c r="G17" t="n">
-        <v>147.9941</v>
+        <v>165.525</v>
       </c>
       <c r="H17" t="n">
-        <v>444.1293</v>
+        <v>426.2548</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.986</v>
+        <v>0.9708</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2972</v>
+        <v>0.6952</v>
       </c>
       <c r="G18" t="n">
-        <v>136.043</v>
+        <v>181.2488</v>
       </c>
       <c r="H18" t="n">
-        <v>404.9604</v>
+        <v>400.6615</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9782</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2956</v>
+        <v>0.6905</v>
       </c>
       <c r="G19" t="n">
-        <v>139.6176</v>
+        <v>163.1583</v>
       </c>
       <c r="H19" t="n">
-        <v>403.8992</v>
+        <v>403.7651</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9474</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3072</v>
+        <v>0.6751</v>
       </c>
       <c r="G20" t="n">
-        <v>141.0133</v>
+        <v>241.593</v>
       </c>
       <c r="H20" t="n">
-        <v>411.7022</v>
+        <v>413.689</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.979</v>
+        <v>0.9727</v>
       </c>
       <c r="F21" t="n">
-        <v>1.301</v>
+        <v>0.677</v>
       </c>
       <c r="G21" t="n">
-        <v>167.9038</v>
+        <v>179.5014</v>
       </c>
       <c r="H21" t="n">
-        <v>407.5318</v>
+        <v>412.4667</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9761</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3071</v>
+        <v>0.6768</v>
       </c>
       <c r="G22" t="n">
-        <v>142.3683</v>
+        <v>167.1863</v>
       </c>
       <c r="H22" t="n">
-        <v>411.6842</v>
+        <v>412.5535</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9775</v>
+        <v>0.9696</v>
       </c>
       <c r="F23" t="n">
-        <v>1.306</v>
+        <v>0.6603</v>
       </c>
       <c r="G23" t="n">
-        <v>171.5005</v>
+        <v>185.9239</v>
       </c>
       <c r="H23" t="n">
-        <v>410.8961</v>
+        <v>422.9936</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9788</v>
+        <v>0.9813</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3036</v>
+        <v>0.6693</v>
       </c>
       <c r="G24" t="n">
-        <v>164.2641</v>
+        <v>155.4918</v>
       </c>
       <c r="H24" t="n">
-        <v>409.3448</v>
+        <v>417.3634</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9849</v>
+        <v>0.9727</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3059</v>
+        <v>0.6619</v>
       </c>
       <c r="G25" t="n">
-        <v>141.9197</v>
+        <v>179.5522</v>
       </c>
       <c r="H25" t="n">
-        <v>410.884</v>
+        <v>421.9798</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9756</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2931</v>
+        <v>0.695</v>
       </c>
       <c r="G26" t="n">
-        <v>136.6344</v>
+        <v>172.0146</v>
       </c>
       <c r="H26" t="n">
-        <v>402.1511</v>
+        <v>400.7883</v>
       </c>
     </row>
     <row r="27">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9862</v>
+        <v>0.9777</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2956</v>
+        <v>0.7025</v>
       </c>
       <c r="G27" t="n">
-        <v>133.391</v>
+        <v>162.0802</v>
       </c>
       <c r="H27" t="n">
-        <v>403.8685</v>
+        <v>395.8321</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9855</v>
+        <v>0.9784</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2961</v>
+        <v>0.7083</v>
       </c>
       <c r="G28" t="n">
-        <v>141.3462</v>
+        <v>160.2378</v>
       </c>
       <c r="H28" t="n">
-        <v>404.2323</v>
+        <v>391.9791</v>
       </c>
     </row>
     <row r="29">
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.985</v>
+        <v>0.9777</v>
       </c>
       <c r="F29" t="n">
-        <v>1.2962</v>
+        <v>0.6856</v>
       </c>
       <c r="G29" t="n">
-        <v>139.2087</v>
+        <v>163.2193</v>
       </c>
       <c r="H29" t="n">
-        <v>404.2812</v>
+        <v>406.8976</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9848</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3078</v>
+        <v>0.6753</v>
       </c>
       <c r="G30" t="n">
-        <v>146.1242</v>
+        <v>166.0244</v>
       </c>
       <c r="H30" t="n">
-        <v>412.1081</v>
+        <v>413.563</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9855</v>
+        <v>0.9719</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2991</v>
+        <v>0.6812</v>
       </c>
       <c r="G31" t="n">
-        <v>141.6188</v>
+        <v>180.7606</v>
       </c>
       <c r="H31" t="n">
-        <v>406.3004</v>
+        <v>409.7552</v>
       </c>
     </row>
     <row r="32">
@@ -1438,16 +1438,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9853</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3114</v>
+        <v>0.6793</v>
       </c>
       <c r="G32" t="n">
-        <v>138.4268</v>
+        <v>168.0027</v>
       </c>
       <c r="H32" t="n">
-        <v>414.52</v>
+        <v>410.9965</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9751</v>
+        <v>0.9767</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3049</v>
+        <v>0.6858</v>
       </c>
       <c r="G33" t="n">
-        <v>179.4309</v>
+        <v>166.0482</v>
       </c>
       <c r="H33" t="n">
-        <v>410.1763</v>
+        <v>406.7938</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9822</v>
+        <v>0.9761</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3016</v>
+        <v>0.7163</v>
       </c>
       <c r="G34" t="n">
-        <v>153.7732</v>
+        <v>169.8654</v>
       </c>
       <c r="H34" t="n">
-        <v>407.9706</v>
+        <v>386.5404</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9832</v>
+        <v>0.9729</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2915</v>
+        <v>0.7167</v>
       </c>
       <c r="G35" t="n">
-        <v>147.616</v>
+        <v>175.9187</v>
       </c>
       <c r="H35" t="n">
-        <v>401.0735</v>
+        <v>386.2848</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9805</v>
+        <v>0.9645</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3052</v>
+        <v>0.7251</v>
       </c>
       <c r="G36" t="n">
-        <v>161.828</v>
+        <v>202.4456</v>
       </c>
       <c r="H36" t="n">
-        <v>410.3696</v>
+        <v>380.5049</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9794</v>
+        <v>0.9778</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2974</v>
+        <v>0.7261</v>
       </c>
       <c r="G37" t="n">
-        <v>164.1887</v>
+        <v>160.7427</v>
       </c>
       <c r="H37" t="n">
-        <v>405.1309</v>
+        <v>379.8163</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9796</v>
+        <v>0.9778</v>
       </c>
       <c r="F38" t="n">
-        <v>1.282</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>156.8508</v>
+        <v>160.8821</v>
       </c>
       <c r="H38" t="n">
-        <v>394.4848</v>
+        <v>375.4514</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9865</v>
+        <v>0.9747</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2747</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>128.3985</v>
+        <v>169.7522</v>
       </c>
       <c r="H39" t="n">
-        <v>389.3393</v>
+        <v>363.9549</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9801</v>
+        <v>0.9759</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2925</v>
+        <v>0.7362</v>
       </c>
       <c r="G40" t="n">
-        <v>160.8333</v>
+        <v>167.2472</v>
       </c>
       <c r="H40" t="n">
-        <v>401.752</v>
+        <v>372.7374</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9766</v>
       </c>
       <c r="F41" t="n">
-        <v>1.2994</v>
+        <v>0.7155</v>
       </c>
       <c r="G41" t="n">
-        <v>153.1325</v>
+        <v>168.2721</v>
       </c>
       <c r="H41" t="n">
-        <v>406.4702</v>
+        <v>387.0952</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9829</v>
+        <v>0.9786</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2915</v>
+        <v>0.7169</v>
       </c>
       <c r="G42" t="n">
-        <v>148.6142</v>
+        <v>160.9389</v>
       </c>
       <c r="H42" t="n">
-        <v>401.0895</v>
+        <v>386.1286</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9767</v>
+        <v>0.9641</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3084</v>
+        <v>0.7242</v>
       </c>
       <c r="G43" t="n">
-        <v>173.4741</v>
+        <v>203.506</v>
       </c>
       <c r="H43" t="n">
-        <v>412.504</v>
+        <v>381.1274</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9792</v>
+        <v>0.9776</v>
       </c>
       <c r="F44" t="n">
-        <v>1.2929</v>
+        <v>0.7248</v>
       </c>
       <c r="G44" t="n">
-        <v>165.5054</v>
+        <v>161.7693</v>
       </c>
       <c r="H44" t="n">
-        <v>402.0329</v>
+        <v>380.7322</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9859</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>1.2801</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>132.5788</v>
+        <v>162.5123</v>
       </c>
       <c r="H45" t="n">
-        <v>393.1609</v>
+        <v>375.4026</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9862</v>
+        <v>0.9792</v>
       </c>
       <c r="F46" t="n">
-        <v>1.2771</v>
+        <v>0.7462</v>
       </c>
       <c r="G46" t="n">
-        <v>129.935</v>
+        <v>156.3195</v>
       </c>
       <c r="H46" t="n">
-        <v>391.0158</v>
+        <v>365.6367</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9848</v>
+        <v>0.9786</v>
       </c>
       <c r="F47" t="n">
-        <v>1.2958</v>
+        <v>0.7321</v>
       </c>
       <c r="G47" t="n">
-        <v>136.2343</v>
+        <v>157.3232</v>
       </c>
       <c r="H47" t="n">
-        <v>404.0427</v>
+        <v>375.647</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9858</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>1.323</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>142.5415</v>
+        <v>202.1061</v>
       </c>
       <c r="H48" t="n">
-        <v>422.1723</v>
+        <v>383.0962</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9791</v>
+        <v>0.9639</v>
       </c>
       <c r="F49" t="n">
-        <v>1.308</v>
+        <v>0.7275</v>
       </c>
       <c r="G49" t="n">
-        <v>170.3968</v>
+        <v>202.0388</v>
       </c>
       <c r="H49" t="n">
-        <v>412.2557</v>
+        <v>378.8231</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9066</v>
+        <v>0.8713</v>
       </c>
       <c r="F50" t="n">
-        <v>1.8788</v>
+        <v>0.0848</v>
       </c>
       <c r="G50" t="n">
-        <v>395.067</v>
+        <v>436.7381</v>
       </c>
       <c r="H50" t="n">
-        <v>696.4018</v>
+        <v>694.2621</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8891</v>
+        <v>0.8582</v>
       </c>
       <c r="F51" t="n">
-        <v>1.8449</v>
+        <v>0.1201</v>
       </c>
       <c r="G51" t="n">
-        <v>406.3867</v>
+        <v>453.7485</v>
       </c>
       <c r="H51" t="n">
-        <v>682.8269</v>
+        <v>680.7548</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8517</v>
+        <v>0.8915</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8569</v>
+        <v>0.1265</v>
       </c>
       <c r="G52" t="n">
-        <v>456.4132</v>
+        <v>411.2126</v>
       </c>
       <c r="H52" t="n">
-        <v>687.6368</v>
+        <v>678.2803</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8965</v>
+        <v>0.9628</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8317</v>
+        <v>0.1851</v>
       </c>
       <c r="G53" t="n">
-        <v>413.1405</v>
+        <v>297.469</v>
       </c>
       <c r="H53" t="n">
-        <v>677.4751</v>
+        <v>655.1142</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8908</v>
+        <v>0.9772</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8035</v>
+        <v>0.2138</v>
       </c>
       <c r="G54" t="n">
-        <v>408.04</v>
+        <v>233.3618</v>
       </c>
       <c r="H54" t="n">
-        <v>665.8663</v>
+        <v>643.509</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8924</v>
+        <v>0.8596</v>
       </c>
       <c r="F55" t="n">
-        <v>1.8749</v>
+        <v>0.0302</v>
       </c>
       <c r="G55" t="n">
-        <v>408.8399</v>
+        <v>453.6293</v>
       </c>
       <c r="H55" t="n">
-        <v>694.8193</v>
+        <v>714.6921</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.9567</v>
       </c>
       <c r="F56" t="n">
-        <v>1.8859</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>448.6497</v>
+        <v>301.9813</v>
       </c>
       <c r="H56" t="n">
-        <v>699.189</v>
+        <v>700.5825</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9049</v>
+        <v>0.9544</v>
       </c>
       <c r="F57" t="n">
-        <v>1.8723</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>398.0218</v>
+        <v>315.7931</v>
       </c>
       <c r="H57" t="n">
-        <v>693.8007</v>
+        <v>695.8438</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8716</v>
+        <v>0.8952</v>
       </c>
       <c r="F58" t="n">
-        <v>1.9276</v>
+        <v>-0.0258</v>
       </c>
       <c r="G58" t="n">
-        <v>418.6837</v>
+        <v>394.0921</v>
       </c>
       <c r="H58" t="n">
-        <v>715.4686</v>
+        <v>735.0513</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8512</v>
+        <v>0.8937</v>
       </c>
       <c r="F59" t="n">
-        <v>1.925</v>
+        <v>-0.0264</v>
       </c>
       <c r="G59" t="n">
-        <v>446.721</v>
+        <v>395.6111</v>
       </c>
       <c r="H59" t="n">
-        <v>714.4402</v>
+        <v>735.2594</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8968</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>1.9268</v>
+        <v>-0.0269</v>
       </c>
       <c r="G60" t="n">
-        <v>387.6151</v>
+        <v>394.8906</v>
       </c>
       <c r="H60" t="n">
-        <v>715.16</v>
+        <v>735.4348</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8447</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>1.9256</v>
+        <v>-0.0188</v>
       </c>
       <c r="G61" t="n">
-        <v>446.8274</v>
+        <v>409.9894</v>
       </c>
       <c r="H61" t="n">
-        <v>714.6968000000001</v>
+        <v>732.5127</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8754</v>
+        <v>0.8804</v>
       </c>
       <c r="F62" t="n">
-        <v>1.9111</v>
+        <v>0.0623</v>
       </c>
       <c r="G62" t="n">
-        <v>423.1379</v>
+        <v>420.8282</v>
       </c>
       <c r="H62" t="n">
-        <v>709.0806</v>
+        <v>702.7521</v>
       </c>
     </row>
     <row r="63">
@@ -2430,16 +2430,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8363</v>
+        <v>0.8374</v>
       </c>
       <c r="F63" t="n">
-        <v>1.9165</v>
+        <v>0.0341</v>
       </c>
       <c r="G63" t="n">
-        <v>463.8268</v>
+        <v>463.6457</v>
       </c>
       <c r="H63" t="n">
-        <v>711.1494</v>
+        <v>713.2333</v>
       </c>
     </row>
     <row r="64">
@@ -2462,16 +2462,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8351</v>
+        <v>0.8373</v>
       </c>
       <c r="F64" t="n">
-        <v>1.9174</v>
+        <v>0.0324</v>
       </c>
       <c r="G64" t="n">
-        <v>463.8705</v>
+        <v>464.0041</v>
       </c>
       <c r="H64" t="n">
-        <v>711.4977</v>
+        <v>713.8874</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8337</v>
+        <v>0.9008</v>
       </c>
       <c r="F65" t="n">
-        <v>1.9197</v>
+        <v>0.035</v>
       </c>
       <c r="G65" t="n">
-        <v>464.8421</v>
+        <v>393.0312</v>
       </c>
       <c r="H65" t="n">
-        <v>712.3913</v>
+        <v>712.9336</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8938</v>
+        <v>0.9742</v>
       </c>
       <c r="F66" t="n">
-        <v>1.8758</v>
+        <v>0.0968</v>
       </c>
       <c r="G66" t="n">
-        <v>409.5181</v>
+        <v>250.8856</v>
       </c>
       <c r="H66" t="n">
-        <v>695.1832000000001</v>
+        <v>689.7114</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9053</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>1.8685</v>
+        <v>0.0806</v>
       </c>
       <c r="G67" t="n">
-        <v>393.9802</v>
+        <v>448.72</v>
       </c>
       <c r="H67" t="n">
-        <v>692.2776</v>
+        <v>695.8833</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9029</v>
+        <v>0.9185</v>
       </c>
       <c r="F68" t="n">
-        <v>1.877</v>
+        <v>0.0839</v>
       </c>
       <c r="G68" t="n">
-        <v>396.5331</v>
+        <v>369.3268</v>
       </c>
       <c r="H68" t="n">
-        <v>695.6547</v>
+        <v>694.6237</v>
       </c>
     </row>
     <row r="69">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9849</v>
+        <v>0.978</v>
       </c>
       <c r="F69" t="n">
-        <v>1.293</v>
+        <v>0.6896</v>
       </c>
       <c r="G69" t="n">
-        <v>139.0723</v>
+        <v>160.2884</v>
       </c>
       <c r="H69" t="n">
-        <v>402.1119</v>
+        <v>404.3139</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9838</v>
+        <v>0.9816</v>
       </c>
       <c r="F70" t="n">
-        <v>1.2933</v>
+        <v>0.6741</v>
       </c>
       <c r="G70" t="n">
-        <v>147.0194</v>
+        <v>152.366</v>
       </c>
       <c r="H70" t="n">
-        <v>402.3024</v>
+        <v>414.3276</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9852</v>
+        <v>0.9769</v>
       </c>
       <c r="F71" t="n">
-        <v>1.3074</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>142.361</v>
+        <v>163.0648</v>
       </c>
       <c r="H71" t="n">
-        <v>411.8588</v>
+        <v>409.9267</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9842</v>
+        <v>0.9777</v>
       </c>
       <c r="F72" t="n">
-        <v>1.2993</v>
+        <v>0.6862</v>
       </c>
       <c r="G72" t="n">
-        <v>144.5152</v>
+        <v>161.491</v>
       </c>
       <c r="H72" t="n">
-        <v>406.3976</v>
+        <v>406.5577</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9842</v>
+        <v>0.9796</v>
       </c>
       <c r="F73" t="n">
-        <v>1.3395</v>
+        <v>0.6619</v>
       </c>
       <c r="G73" t="n">
-        <v>153.1528</v>
+        <v>164.6954</v>
       </c>
       <c r="H73" t="n">
-        <v>432.8146</v>
+        <v>421.9686</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9598</v>
+        <v>0.9823</v>
       </c>
       <c r="F74" t="n">
-        <v>1.3245</v>
+        <v>0.6579</v>
       </c>
       <c r="G74" t="n">
-        <v>218.4171</v>
+        <v>155.818</v>
       </c>
       <c r="H74" t="n">
-        <v>423.1718</v>
+        <v>424.4678</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9821</v>
+        <v>0.9487</v>
       </c>
       <c r="F75" t="n">
-        <v>1.3804</v>
+        <v>0.6301</v>
       </c>
       <c r="G75" t="n">
-        <v>153.353</v>
+        <v>236.6782</v>
       </c>
       <c r="H75" t="n">
-        <v>458.1532</v>
+        <v>441.4006</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9821</v>
+        <v>0.9487</v>
       </c>
       <c r="F76" t="n">
-        <v>1.3804</v>
+        <v>0.6301</v>
       </c>
       <c r="G76" t="n">
-        <v>153.353</v>
+        <v>236.6782</v>
       </c>
       <c r="H76" t="n">
-        <v>458.1532</v>
+        <v>441.4006</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9452</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>1.9166</v>
+        <v>0.0172</v>
       </c>
       <c r="G77" t="n">
-        <v>318.9557</v>
+        <v>392.0138</v>
       </c>
       <c r="H77" t="n">
-        <v>711.1856</v>
+        <v>719.4807</v>
       </c>
     </row>
     <row r="78">
@@ -2910,16 +2910,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8963</v>
+        <v>0.8943</v>
       </c>
       <c r="F78" t="n">
-        <v>1.9186</v>
+        <v>0.016</v>
       </c>
       <c r="G78" t="n">
-        <v>387.8435</v>
+        <v>396.786</v>
       </c>
       <c r="H78" t="n">
-        <v>711.9616</v>
+        <v>719.8984</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8573</v>
+        <v>0.7951</v>
       </c>
       <c r="F79" t="n">
-        <v>1.9213</v>
+        <v>0.0071</v>
       </c>
       <c r="G79" t="n">
-        <v>434.3888</v>
+        <v>492.0161</v>
       </c>
       <c r="H79" t="n">
-        <v>713.0408</v>
+        <v>723.1351</v>
       </c>
     </row>
     <row r="80">
@@ -2974,16 +2974,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8962</v>
+        <v>0.8948</v>
       </c>
       <c r="F80" t="n">
-        <v>1.9165</v>
+        <v>0.0147</v>
       </c>
       <c r="G80" t="n">
-        <v>387.9052</v>
+        <v>396.3307</v>
       </c>
       <c r="H80" t="n">
-        <v>711.1697</v>
+        <v>720.3729</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8444</v>
+        <v>0.8897</v>
       </c>
       <c r="F81" t="n">
-        <v>1.8921</v>
+        <v>0.0382</v>
       </c>
       <c r="G81" t="n">
-        <v>458.4593</v>
+        <v>411.787</v>
       </c>
       <c r="H81" t="n">
-        <v>701.6174999999999</v>
+        <v>711.7380000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8491</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>1.8894</v>
+        <v>0.0262</v>
       </c>
       <c r="G82" t="n">
-        <v>453.8315</v>
+        <v>416.7565</v>
       </c>
       <c r="H82" t="n">
-        <v>700.5838</v>
+        <v>716.1768</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9817</v>
+        <v>0.947</v>
       </c>
       <c r="F83" t="n">
-        <v>1.3809</v>
+        <v>0.6274</v>
       </c>
       <c r="G83" t="n">
-        <v>154.2998</v>
+        <v>239.8819</v>
       </c>
       <c r="H83" t="n">
-        <v>458.4513</v>
+        <v>443.0184</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9817</v>
+        <v>0.9492</v>
       </c>
       <c r="F84" t="n">
-        <v>1.3787</v>
+        <v>0.6294</v>
       </c>
       <c r="G84" t="n">
-        <v>154.2895</v>
+        <v>235.6596</v>
       </c>
       <c r="H84" t="n">
-        <v>457.1123</v>
+        <v>441.8182</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9818</v>
+        <v>0.9468</v>
       </c>
       <c r="F85" t="n">
-        <v>1.3828</v>
+        <v>0.6282</v>
       </c>
       <c r="G85" t="n">
-        <v>154.1882</v>
+        <v>240.5964</v>
       </c>
       <c r="H85" t="n">
-        <v>459.6075</v>
+        <v>442.504</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9846</v>
+        <v>0.9574</v>
       </c>
       <c r="F86" t="n">
-        <v>1.301</v>
+        <v>0.6784</v>
       </c>
       <c r="G86" t="n">
-        <v>141.0575</v>
+        <v>219.0557</v>
       </c>
       <c r="H86" t="n">
-        <v>407.5843</v>
+        <v>411.5843</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9808</v>
+        <v>0.9577</v>
       </c>
       <c r="F87" t="n">
-        <v>1.309</v>
+        <v>0.6868</v>
       </c>
       <c r="G87" t="n">
-        <v>157.6598</v>
+        <v>218.435</v>
       </c>
       <c r="H87" t="n">
-        <v>412.9119</v>
+        <v>406.1311</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.979</v>
+        <v>0.9512</v>
       </c>
       <c r="F88" t="n">
-        <v>1.3115</v>
+        <v>0.6675</v>
       </c>
       <c r="G88" t="n">
-        <v>162.8857</v>
+        <v>233.6998</v>
       </c>
       <c r="H88" t="n">
-        <v>414.6046</v>
+        <v>418.4547</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9786</v>
+        <v>0.9768</v>
       </c>
       <c r="F89" t="n">
-        <v>1.3325</v>
+        <v>0.6633</v>
       </c>
       <c r="G89" t="n">
-        <v>166.0664</v>
+        <v>166.8366</v>
       </c>
       <c r="H89" t="n">
-        <v>428.3391</v>
+        <v>421.0985</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9767</v>
+        <v>0.9641</v>
       </c>
       <c r="F90" t="n">
-        <v>1.3084</v>
+        <v>0.7242</v>
       </c>
       <c r="G90" t="n">
-        <v>173.4741</v>
+        <v>203.5076</v>
       </c>
       <c r="H90" t="n">
-        <v>412.5228</v>
+        <v>381.1123</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9792</v>
+        <v>0.9776</v>
       </c>
       <c r="F91" t="n">
-        <v>1.2929</v>
+        <v>0.7248</v>
       </c>
       <c r="G91" t="n">
-        <v>165.5054</v>
+        <v>161.7629</v>
       </c>
       <c r="H91" t="n">
-        <v>402.034</v>
+        <v>380.7414</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.979</v>
+        <v>0.9512</v>
       </c>
       <c r="F92" t="n">
-        <v>1.3115</v>
+        <v>0.6675</v>
       </c>
       <c r="G92" t="n">
-        <v>162.8857</v>
+        <v>233.6998</v>
       </c>
       <c r="H92" t="n">
-        <v>414.6046</v>
+        <v>418.4547</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9792</v>
+        <v>0.9776</v>
       </c>
       <c r="F93" t="n">
-        <v>1.2929</v>
+        <v>0.7248</v>
       </c>
       <c r="G93" t="n">
-        <v>165.5054</v>
+        <v>161.7629</v>
       </c>
       <c r="H93" t="n">
-        <v>402.034</v>
+        <v>380.7414</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9821</v>
+        <v>0.9393</v>
       </c>
       <c r="F94" t="n">
-        <v>1.4083</v>
+        <v>0.6384</v>
       </c>
       <c r="G94" t="n">
-        <v>161.3524</v>
+        <v>256.6862</v>
       </c>
       <c r="H94" t="n">
-        <v>474.6909</v>
+        <v>436.4298</v>
       </c>
     </row>
     <row r="95">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7972</v>
+        <v>0.7448</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1432</v>
+        <v>-0.0984</v>
       </c>
       <c r="G95" t="n">
-        <v>532.3154</v>
+        <v>547.5359999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>794.253</v>
+        <v>760.5928</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9823</v>
+        <v>0.9397</v>
       </c>
       <c r="F96" t="n">
-        <v>1.4091</v>
+        <v>0.6387</v>
       </c>
       <c r="G96" t="n">
-        <v>160.2295</v>
+        <v>255.8908</v>
       </c>
       <c r="H96" t="n">
-        <v>475.1086</v>
+        <v>436.2</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9367</v>
       </c>
       <c r="F97" t="n">
-        <v>1.4084</v>
+        <v>0.6431</v>
       </c>
       <c r="G97" t="n">
-        <v>159.8229</v>
+        <v>262.6263</v>
       </c>
       <c r="H97" t="n">
-        <v>474.7348</v>
+        <v>433.5801</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9873</v>
+        <v>0.9774</v>
       </c>
       <c r="F98" t="n">
-        <v>1.2992</v>
+        <v>0.7025</v>
       </c>
       <c r="G98" t="n">
-        <v>139.8011</v>
+        <v>172.543</v>
       </c>
       <c r="H98" t="n">
-        <v>406.348</v>
+        <v>395.8352</v>
       </c>
     </row>
     <row r="99">
@@ -3582,16 +3582,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9869</v>
+        <v>0.9836</v>
       </c>
       <c r="F99" t="n">
-        <v>1.296</v>
+        <v>0.7057</v>
       </c>
       <c r="G99" t="n">
-        <v>138.6736</v>
+        <v>149.1084</v>
       </c>
       <c r="H99" t="n">
-        <v>404.15</v>
+        <v>393.6777</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9869</v>
+        <v>0.9771</v>
       </c>
       <c r="F100" t="n">
-        <v>1.2978</v>
+        <v>0.7063</v>
       </c>
       <c r="G100" t="n">
-        <v>139.1557</v>
+        <v>168.4636</v>
       </c>
       <c r="H100" t="n">
-        <v>405.3764</v>
+        <v>393.3255</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9866</v>
+        <v>0.9811</v>
       </c>
       <c r="F101" t="n">
-        <v>1.3027</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="G101" t="n">
-        <v>140.6831</v>
+        <v>152.6099</v>
       </c>
       <c r="H101" t="n">
-        <v>408.736</v>
+        <v>390.0407</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9862</v>
+        <v>0.9679</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3078</v>
+        <v>0.716</v>
       </c>
       <c r="G102" t="n">
-        <v>141.0485</v>
+        <v>196.3631</v>
       </c>
       <c r="H102" t="n">
-        <v>412.1191</v>
+        <v>386.7409</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9875</v>
+        <v>0.9785</v>
       </c>
       <c r="F103" t="n">
-        <v>1.3033</v>
+        <v>0.705</v>
       </c>
       <c r="G103" t="n">
-        <v>138.6462</v>
+        <v>172.4398</v>
       </c>
       <c r="H103" t="n">
-        <v>409.0801</v>
+        <v>394.1779</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9869</v>
+        <v>0.9707</v>
       </c>
       <c r="F104" t="n">
-        <v>1.2997</v>
+        <v>0.719</v>
       </c>
       <c r="G104" t="n">
-        <v>140.6354</v>
+        <v>187.2553</v>
       </c>
       <c r="H104" t="n">
-        <v>406.6542</v>
+        <v>384.6749</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9771</v>
+        <v>0.9822</v>
       </c>
       <c r="F105" t="n">
-        <v>1.298</v>
+        <v>0.7046</v>
       </c>
       <c r="G105" t="n">
-        <v>176.2734</v>
+        <v>151.1073</v>
       </c>
       <c r="H105" t="n">
-        <v>405.5289</v>
+        <v>394.4169</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9868</v>
+        <v>0.9761</v>
       </c>
       <c r="F106" t="n">
-        <v>1.2973</v>
+        <v>0.7117</v>
       </c>
       <c r="G106" t="n">
-        <v>140.0551</v>
+        <v>174.3902</v>
       </c>
       <c r="H106" t="n">
-        <v>405.0721</v>
+        <v>389.6654</v>
       </c>
     </row>
     <row r="107">
@@ -3838,16 +3838,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9863</v>
+        <v>0.9833</v>
       </c>
       <c r="F107" t="n">
-        <v>1.303</v>
+        <v>0.6995</v>
       </c>
       <c r="G107" t="n">
-        <v>140.7095</v>
+        <v>150.3021</v>
       </c>
       <c r="H107" t="n">
-        <v>408.9332</v>
+        <v>397.8351</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.975</v>
+        <v>0.9842</v>
       </c>
       <c r="F108" t="n">
-        <v>1.3596</v>
+        <v>0.6683</v>
       </c>
       <c r="G108" t="n">
-        <v>191.799</v>
+        <v>152.9145</v>
       </c>
       <c r="H108" t="n">
-        <v>445.4706</v>
+        <v>417.9635</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9839</v>
+        <v>0.9827</v>
       </c>
       <c r="F109" t="n">
-        <v>1.3062</v>
+        <v>0.7129</v>
       </c>
       <c r="G109" t="n">
-        <v>155.5727</v>
+        <v>156.4519</v>
       </c>
       <c r="H109" t="n">
-        <v>411.0667</v>
+        <v>388.8337</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9846</v>
+        <v>0.9621</v>
       </c>
       <c r="F110" t="n">
-        <v>1.3061</v>
+        <v>0.6927</v>
       </c>
       <c r="G110" t="n">
-        <v>142.7864</v>
+        <v>217.4855</v>
       </c>
       <c r="H110" t="n">
-        <v>410.9707</v>
+        <v>402.33</v>
       </c>
     </row>
     <row r="111">
@@ -3966,16 +3966,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F111" t="n">
-        <v>1.307</v>
+        <v>0.6894</v>
       </c>
       <c r="G111" t="n">
-        <v>171.3365</v>
+        <v>182.2988</v>
       </c>
       <c r="H111" t="n">
-        <v>411.6282</v>
+        <v>404.4567</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9848</v>
+        <v>0.9818</v>
       </c>
       <c r="F112" t="n">
-        <v>1.3562</v>
+        <v>0.6698</v>
       </c>
       <c r="G112" t="n">
-        <v>154.3992</v>
+        <v>159.635</v>
       </c>
       <c r="H112" t="n">
-        <v>443.3702</v>
+        <v>417.0223</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.984</v>
+        <v>0.9823</v>
       </c>
       <c r="F113" t="n">
-        <v>1.3068</v>
+        <v>0.7106</v>
       </c>
       <c r="G113" t="n">
-        <v>155.5095</v>
+        <v>156.9593</v>
       </c>
       <c r="H113" t="n">
-        <v>411.485</v>
+        <v>390.3949</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9798</v>
+        <v>0.9816</v>
       </c>
       <c r="F114" t="n">
-        <v>1.3073</v>
+        <v>0.6964</v>
       </c>
       <c r="G114" t="n">
-        <v>162.1036</v>
+        <v>154.9675</v>
       </c>
       <c r="H114" t="n">
-        <v>411.7709</v>
+        <v>399.8547</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9859</v>
+        <v>0.9767</v>
       </c>
       <c r="F115" t="n">
-        <v>1.3057</v>
+        <v>0.6868</v>
       </c>
       <c r="G115" t="n">
-        <v>146.6426</v>
+        <v>175.3187</v>
       </c>
       <c r="H115" t="n">
-        <v>410.7345</v>
+        <v>406.1496</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8855</v>
+        <v>0.8093</v>
       </c>
       <c r="F116" t="n">
-        <v>1.9226</v>
+        <v>0.0372</v>
       </c>
       <c r="G116" t="n">
-        <v>407.6548</v>
+        <v>489.8407</v>
       </c>
       <c r="H116" t="n">
-        <v>713.5441</v>
+        <v>712.1077</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8837</v>
+        <v>0.8315</v>
       </c>
       <c r="F117" t="n">
-        <v>1.9226</v>
+        <v>0.0399</v>
       </c>
       <c r="G117" t="n">
-        <v>408.8045</v>
+        <v>471.5473</v>
       </c>
       <c r="H117" t="n">
-        <v>713.5264</v>
+        <v>711.1053000000001</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9771</v>
+        <v>0.9822</v>
       </c>
       <c r="F118" t="n">
-        <v>1.298</v>
+        <v>0.7046</v>
       </c>
       <c r="G118" t="n">
-        <v>176.2734</v>
+        <v>151.1073</v>
       </c>
       <c r="H118" t="n">
-        <v>405.5289</v>
+        <v>394.4169</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.984</v>
+        <v>0.9823</v>
       </c>
       <c r="F119" t="n">
-        <v>1.3068</v>
+        <v>0.7106</v>
       </c>
       <c r="G119" t="n">
-        <v>155.5095</v>
+        <v>156.9593</v>
       </c>
       <c r="H119" t="n">
-        <v>411.485</v>
+        <v>390.3949</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9296</v>
       </c>
       <c r="F120" t="n">
-        <v>1.3248</v>
+        <v>0.6788</v>
       </c>
       <c r="G120" t="n">
-        <v>195.4517</v>
+        <v>274.4985</v>
       </c>
       <c r="H120" t="n">
-        <v>423.3378</v>
+        <v>411.3026</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9296</v>
       </c>
       <c r="F121" t="n">
-        <v>1.3248</v>
+        <v>0.6788</v>
       </c>
       <c r="G121" t="n">
-        <v>195.4517</v>
+        <v>274.4985</v>
       </c>
       <c r="H121" t="n">
-        <v>423.3378</v>
+        <v>411.3026</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9651</v>
+        <v>0.9468</v>
       </c>
       <c r="F122" t="n">
-        <v>1.2758</v>
+        <v>0.7106</v>
       </c>
       <c r="G122" t="n">
-        <v>199.4662</v>
+        <v>238.0296</v>
       </c>
       <c r="H122" t="n">
-        <v>390.0987</v>
+        <v>390.4458</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.984</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3076</v>
+        <v>0.7085</v>
       </c>
       <c r="G123" t="n">
-        <v>155.5907</v>
+        <v>156.2355</v>
       </c>
       <c r="H123" t="n">
-        <v>412.0081</v>
+        <v>391.807</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9866</v>
+        <v>0.9516</v>
       </c>
       <c r="F124" t="n">
-        <v>1.3081</v>
+        <v>0.6976</v>
       </c>
       <c r="G124" t="n">
-        <v>141.4007</v>
+        <v>240.7605</v>
       </c>
       <c r="H124" t="n">
-        <v>412.3005</v>
+        <v>399.085</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9403</v>
       </c>
       <c r="F125" t="n">
-        <v>1.415</v>
+        <v>0.6433</v>
       </c>
       <c r="G125" t="n">
-        <v>209.6701</v>
+        <v>254.677</v>
       </c>
       <c r="H125" t="n">
-        <v>478.5414</v>
+        <v>433.4487</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9856</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>1.2935</v>
+        <v>0.708</v>
       </c>
       <c r="G126" t="n">
-        <v>135.9838</v>
+        <v>188.6952</v>
       </c>
       <c r="H126" t="n">
-        <v>402.4174</v>
+        <v>392.1861</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.7909</v>
+        <v>0.8658</v>
       </c>
       <c r="F127" t="n">
-        <v>1.9984</v>
+        <v>-0.011</v>
       </c>
       <c r="G127" t="n">
-        <v>506.7163</v>
+        <v>434.6959</v>
       </c>
       <c r="H127" t="n">
-        <v>742.2674</v>
+        <v>729.7065</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9836</v>
+        <v>0.9674</v>
       </c>
       <c r="F128" t="n">
-        <v>1.3106</v>
+        <v>0.6915</v>
       </c>
       <c r="G128" t="n">
-        <v>146.1011</v>
+        <v>192.5542</v>
       </c>
       <c r="H128" t="n">
-        <v>413.9786</v>
+        <v>403.073</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>1.3145</v>
+        <v>0.6966</v>
       </c>
       <c r="G129" t="n">
-        <v>141.6096</v>
+        <v>193.0858</v>
       </c>
       <c r="H129" t="n">
-        <v>416.5998</v>
+        <v>399.7422</v>
       </c>
     </row>
     <row r="130">
@@ -4570,20 +4570,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.981</v>
       </c>
       <c r="F130" t="n">
-        <v>1.3161</v>
+        <v>0.6858</v>
       </c>
       <c r="G130" t="n">
-        <v>138.9333</v>
+        <v>156.7863</v>
       </c>
       <c r="H130" t="n">
-        <v>417.6493</v>
+        <v>406.81</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.986</v>
+        <v>0.9729</v>
       </c>
       <c r="F131" t="n">
-        <v>1.3164</v>
+        <v>0.6844</v>
       </c>
       <c r="G131" t="n">
-        <v>140.5252</v>
+        <v>178.483</v>
       </c>
       <c r="H131" t="n">
-        <v>417.8385</v>
+        <v>407.6742</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.985</v>
+        <v>0.9683</v>
       </c>
       <c r="F132" t="n">
-        <v>1.2952</v>
+        <v>0.6973</v>
       </c>
       <c r="G132" t="n">
-        <v>138.5526</v>
+        <v>189.2847</v>
       </c>
       <c r="H132" t="n">
-        <v>403.6386</v>
+        <v>399.2675</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9855</v>
+        <v>0.9676</v>
       </c>
       <c r="F133" t="n">
-        <v>1.302</v>
+        <v>0.6975</v>
       </c>
       <c r="G133" t="n">
-        <v>136.4423</v>
+        <v>191.8832</v>
       </c>
       <c r="H133" t="n">
-        <v>408.2317</v>
+        <v>399.1673</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9851</v>
+        <v>0.9677</v>
       </c>
       <c r="F134" t="n">
-        <v>1.3014</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="G134" t="n">
-        <v>138.6933</v>
+        <v>191.6482</v>
       </c>
       <c r="H134" t="n">
-        <v>407.8127</v>
+        <v>399.4102</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9846</v>
+        <v>0.9668</v>
       </c>
       <c r="F135" t="n">
-        <v>1.3047</v>
+        <v>0.7006</v>
       </c>
       <c r="G135" t="n">
-        <v>141.4099</v>
+        <v>193.5016</v>
       </c>
       <c r="H135" t="n">
-        <v>410.0399</v>
+        <v>397.1012</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.974</v>
       </c>
       <c r="F136" t="n">
-        <v>1.3102</v>
+        <v>0.6883</v>
       </c>
       <c r="G136" t="n">
-        <v>141.3175</v>
+        <v>175.9283</v>
       </c>
       <c r="H136" t="n">
-        <v>413.761</v>
+        <v>405.1785</v>
       </c>
     </row>
     <row r="137">
@@ -4798,16 +4798,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9849</v>
+        <v>0.9811</v>
       </c>
       <c r="F137" t="n">
-        <v>1.2892</v>
+        <v>0.7145</v>
       </c>
       <c r="G137" t="n">
-        <v>137.4266</v>
+        <v>151.4758</v>
       </c>
       <c r="H137" t="n">
-        <v>399.4991</v>
+        <v>387.7634</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9837</v>
+        <v>0.9822</v>
       </c>
       <c r="F138" t="n">
-        <v>1.2838</v>
+        <v>0.7098</v>
       </c>
       <c r="G138" t="n">
-        <v>141.4904</v>
+        <v>148.3221</v>
       </c>
       <c r="H138" t="n">
-        <v>395.7546</v>
+        <v>390.9617</v>
       </c>
     </row>
     <row r="139">
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9846</v>
+        <v>0.9813</v>
       </c>
       <c r="F139" t="n">
-        <v>1.2843</v>
+        <v>0.7144</v>
       </c>
       <c r="G139" t="n">
-        <v>139.8186</v>
+        <v>149.8609</v>
       </c>
       <c r="H139" t="n">
-        <v>396.0884</v>
+        <v>387.8394</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9804</v>
+        <v>0.9849</v>
       </c>
       <c r="F140" t="n">
-        <v>1.2769</v>
+        <v>0.7084</v>
       </c>
       <c r="G140" t="n">
-        <v>159.6285</v>
+        <v>145.4792</v>
       </c>
       <c r="H140" t="n">
-        <v>390.8841</v>
+        <v>391.8688</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9828</v>
+        <v>0.9823</v>
       </c>
       <c r="F141" t="n">
-        <v>1.2749</v>
+        <v>0.7176</v>
       </c>
       <c r="G141" t="n">
-        <v>147.976</v>
+        <v>151.1435</v>
       </c>
       <c r="H141" t="n">
-        <v>389.4902</v>
+        <v>385.6411</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9837</v>
+        <v>0.9822</v>
       </c>
       <c r="F142" t="n">
-        <v>1.2838</v>
+        <v>0.7098</v>
       </c>
       <c r="G142" t="n">
-        <v>141.4904</v>
+        <v>148.3221</v>
       </c>
       <c r="H142" t="n">
-        <v>395.7546</v>
+        <v>390.9617</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9744</v>
       </c>
       <c r="F143" t="n">
-        <v>1.2824</v>
+        <v>0.7191</v>
       </c>
       <c r="G143" t="n">
-        <v>169.0301</v>
+        <v>174.18</v>
       </c>
       <c r="H143" t="n">
-        <v>394.7946</v>
+        <v>384.6537</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9847</v>
+        <v>0.974</v>
       </c>
       <c r="F144" t="n">
-        <v>1.2901</v>
+        <v>0.7121</v>
       </c>
       <c r="G144" t="n">
-        <v>139.6542</v>
+        <v>174.4959</v>
       </c>
       <c r="H144" t="n">
-        <v>400.0851</v>
+        <v>389.392</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9828</v>
+        <v>0.9823</v>
       </c>
       <c r="F145" t="n">
-        <v>1.2749</v>
+        <v>0.7176</v>
       </c>
       <c r="G145" t="n">
-        <v>147.976</v>
+        <v>151.1435</v>
       </c>
       <c r="H145" t="n">
-        <v>389.4902</v>
+        <v>385.6411</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.7921</v>
+        <v>0.8665</v>
       </c>
       <c r="F146" t="n">
-        <v>1.9966</v>
+        <v>-0.0141</v>
       </c>
       <c r="G146" t="n">
-        <v>505.7545</v>
+        <v>431.6481</v>
       </c>
       <c r="H146" t="n">
-        <v>741.6064</v>
+        <v>730.8424</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.7936</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="F147" t="n">
-        <v>1.9945</v>
+        <v>-0.0035</v>
       </c>
       <c r="G147" t="n">
-        <v>504.3034</v>
+        <v>432.61</v>
       </c>
       <c r="H147" t="n">
-        <v>740.8022999999999</v>
+        <v>727.0154</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.7938</v>
+        <v>0.8692</v>
       </c>
       <c r="F148" t="n">
-        <v>1.9971</v>
+        <v>0.0062</v>
       </c>
       <c r="G148" t="n">
-        <v>504.5749</v>
+        <v>430.2521</v>
       </c>
       <c r="H148" t="n">
-        <v>741.7617</v>
+        <v>723.4962</v>
       </c>
     </row>
     <row r="149">
@@ -5178,20 +5178,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8454</v>
+        <v>0.8713</v>
       </c>
       <c r="F149" t="n">
-        <v>1.9981</v>
+        <v>-0.0019</v>
       </c>
       <c r="G149" t="n">
-        <v>457.171</v>
+        <v>429.4958</v>
       </c>
       <c r="H149" t="n">
-        <v>742.1499</v>
+        <v>726.4392</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.7904</v>
+        <v>0.8666</v>
       </c>
       <c r="F150" t="n">
-        <v>1.9966</v>
+        <v>-0.0111</v>
       </c>
       <c r="G150" t="n">
-        <v>507.0519</v>
+        <v>433.2897</v>
       </c>
       <c r="H150" t="n">
-        <v>741.5744</v>
+        <v>729.7429</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.7925</v>
+        <v>0.8662</v>
       </c>
       <c r="F151" t="n">
-        <v>1.9975</v>
+        <v>-0.0119</v>
       </c>
       <c r="G151" t="n">
-        <v>505.8393</v>
+        <v>433.9615</v>
       </c>
       <c r="H151" t="n">
-        <v>741.9429</v>
+        <v>730.0456</v>
       </c>
     </row>
     <row r="152">
@@ -5274,20 +5274,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.7936</v>
+        <v>0.8668</v>
       </c>
       <c r="F152" t="n">
-        <v>1.9983</v>
+        <v>-0.01</v>
       </c>
       <c r="G152" t="n">
-        <v>505.1203</v>
+        <v>433.352</v>
       </c>
       <c r="H152" t="n">
-        <v>742.2204</v>
+        <v>729.3536</v>
       </c>
     </row>
     <row r="153">
@@ -5306,20 +5306,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.793</v>
+        <v>0.8653</v>
       </c>
       <c r="F153" t="n">
-        <v>1.9993</v>
+        <v>-0.0132</v>
       </c>
       <c r="G153" t="n">
-        <v>505.5168</v>
+        <v>433.2837</v>
       </c>
       <c r="H153" t="n">
-        <v>742.6058</v>
+        <v>730.5221</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.7916</v>
+        <v>0.8687</v>
       </c>
       <c r="F154" t="n">
-        <v>1.9971</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>506.358</v>
+        <v>431.1266</v>
       </c>
       <c r="H154" t="n">
-        <v>741.7726</v>
+        <v>728.9177</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.9483</v>
       </c>
       <c r="F155" t="n">
-        <v>1.9028</v>
+        <v>0.0378</v>
       </c>
       <c r="G155" t="n">
-        <v>460.0744</v>
+        <v>331.7794</v>
       </c>
       <c r="H155" t="n">
-        <v>705.8313000000001</v>
+        <v>711.8777</v>
       </c>
     </row>
     <row r="156">
@@ -5402,20 +5402,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.8404</v>
+        <v>0.9475</v>
       </c>
       <c r="F156" t="n">
-        <v>1.9159</v>
+        <v>0.0216</v>
       </c>
       <c r="G156" t="n">
-        <v>464.1396</v>
+        <v>332.8872</v>
       </c>
       <c r="H156" t="n">
-        <v>710.914</v>
+        <v>717.8467000000001</v>
       </c>
     </row>
     <row r="157">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8399</v>
+        <v>0.8415</v>
       </c>
       <c r="F157" t="n">
-        <v>1.9117</v>
+        <v>0.0275</v>
       </c>
       <c r="G157" t="n">
-        <v>463.7489</v>
+        <v>469.1957</v>
       </c>
       <c r="H157" t="n">
-        <v>709.3092</v>
+        <v>715.6999</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8541</v>
+        <v>0.9477</v>
       </c>
       <c r="F158" t="n">
-        <v>1.8782</v>
+        <v>0.0922</v>
       </c>
       <c r="G158" t="n">
-        <v>457.4726</v>
+        <v>325.2429</v>
       </c>
       <c r="H158" t="n">
-        <v>696.1299</v>
+        <v>691.4497</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9872</v>
+        <v>0.9775</v>
       </c>
       <c r="F159" t="n">
-        <v>1.2718</v>
+        <v>0.7095</v>
       </c>
       <c r="G159" t="n">
-        <v>128.4378</v>
+        <v>164.7739</v>
       </c>
       <c r="H159" t="n">
-        <v>387.3087</v>
+        <v>391.1273</v>
       </c>
     </row>
     <row r="160">
@@ -5530,20 +5530,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8738</v>
       </c>
       <c r="F160" t="n">
-        <v>1.9716</v>
+        <v>-0.0248</v>
       </c>
       <c r="G160" t="n">
-        <v>451.1679</v>
+        <v>432.9725</v>
       </c>
       <c r="H160" t="n">
-        <v>732.2422</v>
+        <v>734.684</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8462</v>
+        <v>0.8739</v>
       </c>
       <c r="F161" t="n">
-        <v>1.9783</v>
+        <v>-0.0265</v>
       </c>
       <c r="G161" t="n">
-        <v>456.7384</v>
+        <v>433.7158</v>
       </c>
       <c r="H161" t="n">
-        <v>734.7424</v>
+        <v>735.2908</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9876</v>
+        <v>0.9764</v>
       </c>
       <c r="F162" t="n">
-        <v>1.2791</v>
+        <v>0.699</v>
       </c>
       <c r="G162" t="n">
-        <v>129.0899</v>
+        <v>166.8255</v>
       </c>
       <c r="H162" t="n">
-        <v>392.449</v>
+        <v>398.1835</v>
       </c>
     </row>
     <row r="163">
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9856</v>
+        <v>0.9838</v>
       </c>
       <c r="F163" t="n">
-        <v>1.2923</v>
+        <v>0.7176</v>
       </c>
       <c r="G163" t="n">
-        <v>137.4742</v>
+        <v>143.1894</v>
       </c>
       <c r="H163" t="n">
-        <v>401.6111</v>
+        <v>385.6869</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9804</v>
+        <v>0.9849</v>
       </c>
       <c r="F164" t="n">
-        <v>1.2778</v>
+        <v>0.7085</v>
       </c>
       <c r="G164" t="n">
-        <v>159.6571</v>
+        <v>145.1374</v>
       </c>
       <c r="H164" t="n">
-        <v>391.529</v>
+        <v>391.8299</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9403</v>
       </c>
       <c r="F165" t="n">
-        <v>1.415</v>
+        <v>0.6433</v>
       </c>
       <c r="G165" t="n">
-        <v>209.6701</v>
+        <v>254.677</v>
       </c>
       <c r="H165" t="n">
-        <v>478.5414</v>
+        <v>433.4487</v>
       </c>
     </row>
     <row r="166">
@@ -5726,16 +5726,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7473</v>
       </c>
       <c r="F166" t="n">
-        <v>2.1431</v>
+        <v>-0.1007</v>
       </c>
       <c r="G166" t="n">
-        <v>531.7619</v>
+        <v>544.875</v>
       </c>
       <c r="H166" t="n">
-        <v>794.2306</v>
+        <v>761.3928</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9863</v>
+        <v>0.9812</v>
       </c>
       <c r="F167" t="n">
-        <v>1.2818</v>
+        <v>0.7175</v>
       </c>
       <c r="G167" t="n">
-        <v>135.1389</v>
+        <v>150.34</v>
       </c>
       <c r="H167" t="n">
-        <v>394.3533</v>
+        <v>385.7478</v>
       </c>
     </row>
     <row r="168">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9871</v>
+        <v>0.9532</v>
       </c>
       <c r="F168" t="n">
-        <v>1.2625</v>
+        <v>0.7079</v>
       </c>
       <c r="G168" t="n">
-        <v>133.0159</v>
+        <v>238.4095</v>
       </c>
       <c r="H168" t="n">
-        <v>380.6285</v>
+        <v>392.2098</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.984</v>
+        <v>0.9553</v>
       </c>
       <c r="F169" t="n">
-        <v>1.326</v>
+        <v>0.6645</v>
       </c>
       <c r="G169" t="n">
-        <v>144.015</v>
+        <v>222.0146</v>
       </c>
       <c r="H169" t="n">
-        <v>424.1137</v>
+        <v>420.385</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9847</v>
+        <v>0.9836</v>
       </c>
       <c r="F170" t="n">
-        <v>1.3527</v>
+        <v>0.6514</v>
       </c>
       <c r="G170" t="n">
-        <v>147.8144</v>
+        <v>155.0402</v>
       </c>
       <c r="H170" t="n">
-        <v>441.1947</v>
+        <v>428.4779</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9798</v>
       </c>
       <c r="F171" t="n">
-        <v>1.2993</v>
+        <v>0.7279</v>
       </c>
       <c r="G171" t="n">
-        <v>144.9906</v>
+        <v>157.9057</v>
       </c>
       <c r="H171" t="n">
-        <v>406.369</v>
+        <v>378.5401</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9808</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>1.2908</v>
+        <v>0.7264</v>
       </c>
       <c r="G172" t="n">
-        <v>155.307</v>
+        <v>172.6594</v>
       </c>
       <c r="H172" t="n">
-        <v>400.6169</v>
+        <v>379.6163</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/total.carotene/RANDOMSEARCH_DETAILS_total.carotene.xlsx
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -3012,7 +3012,7 @@
         <v>0.0382</v>
       </c>
       <c r="G81" t="n">
-        <v>411.787</v>
+        <v>411.7343</v>
       </c>
       <c r="H81" t="n">
         <v>711.7380000000001</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
